--- a/Theo dõi/T1 2026 02-01.xlsx
+++ b/Theo dõi/T1 2026 02-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26BB922-F7C8-46F2-A89B-EA559088A056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DE3FD2-0981-41AC-B839-3CE30A0D846F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="13" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="16" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="biển số xe" sheetId="26" r:id="rId1"/>
@@ -41,6 +41,9 @@
     <sheet name="24-01" sheetId="30" r:id="rId26"/>
     <sheet name="25-01" sheetId="31" r:id="rId27"/>
     <sheet name="26-01" sheetId="32" r:id="rId28"/>
+    <sheet name="27-01" sheetId="33" r:id="rId29"/>
+    <sheet name="28-01" sheetId="34" r:id="rId30"/>
+    <sheet name="29-01" sheetId="35" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3440" uniqueCount="202">
   <si>
     <t>STT</t>
   </si>
@@ -628,6 +631,48 @@
   <si>
     <t>DOANH THU 26/01/2026</t>
   </si>
+  <si>
+    <t>Đức Anh</t>
+  </si>
+  <si>
+    <t>chia 5 5 thọt 70</t>
+  </si>
+  <si>
+    <t>DOANH THU 27/01/2026</t>
+  </si>
+  <si>
+    <t>Nạp tiền trễ</t>
+  </si>
+  <si>
+    <t>nợ bác thạo 160</t>
+  </si>
+  <si>
+    <t>thọt 4k</t>
+  </si>
+  <si>
+    <t>Xin bác Kim nghỉ 1 hôm</t>
+  </si>
+  <si>
+    <t>Trọng Tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 5 </t>
+  </si>
+  <si>
+    <t>DOANH THU 28/01/2026</t>
+  </si>
+  <si>
+    <t>cần bù thêm 50k</t>
+  </si>
+  <si>
+    <t>DOANH THU 29/01/2026</t>
+  </si>
+  <si>
+    <t>Chú thành</t>
+  </si>
+  <si>
+    <t>5 5 thọt 100</t>
+  </si>
 </sst>
 </file>
 
@@ -873,7 +918,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -989,6 +1034,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -1158,7 +1209,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1631,6 +1682,30 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4720,32 +4795,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -5412,20 +5487,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>16918000</v>
@@ -5562,32 +5637,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -6245,20 +6320,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -6407,18 +6482,18 @@
     </row>
     <row r="2" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -6427,18 +6502,18 @@
     </row>
     <row r="3" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -6532,7 +6607,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="189" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="98">
@@ -6577,7 +6652,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="180"/>
+      <c r="A8" s="190"/>
       <c r="B8" s="70">
         <f>B7+1</f>
         <v>2</v>
@@ -6624,7 +6699,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="180"/>
+      <c r="A9" s="190"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B12" si="1">B8+1</f>
         <v>3</v>
@@ -6667,7 +6742,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="180"/>
+      <c r="A10" s="190"/>
       <c r="B10" s="70">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6706,7 +6781,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="180"/>
+      <c r="A11" s="190"/>
       <c r="B11" s="64">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6749,7 +6824,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="180"/>
+      <c r="A12" s="190"/>
       <c r="B12" s="70">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6792,7 +6867,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="180"/>
+      <c r="A13" s="190"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -6828,7 +6903,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64"/>
@@ -6848,7 +6923,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <v>1</v>
       </c>
@@ -6889,7 +6964,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f>B16+1</f>
         <v>2</v>
@@ -6931,7 +7006,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" ref="B18:B26" si="2">B17+1</f>
         <v>3</v>
@@ -6973,7 +7048,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7015,7 +7090,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7057,7 +7132,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7099,7 +7174,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7141,7 +7216,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7183,7 +7258,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7225,7 +7300,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="181"/>
+      <c r="A25" s="191"/>
       <c r="B25" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7267,7 +7342,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="181"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7315,30 +7390,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="177" t="s">
+      <c r="H28" s="187" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="178"/>
+      <c r="I28" s="188"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29569000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="177" t="s">
+      <c r="H29" s="187" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="178"/>
+      <c r="I29" s="188"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17731000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="177" t="s">
+      <c r="H30" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="178"/>
+      <c r="I30" s="188"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17731000</v>
@@ -7419,18 +7494,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -7524,7 +7599,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="189" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -7570,7 +7645,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="180"/>
+      <c r="A8" s="190"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -7615,7 +7690,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="180"/>
+      <c r="A9" s="190"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -7654,7 +7729,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="180"/>
+      <c r="A10" s="190"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -7697,7 +7772,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="180"/>
+      <c r="A11" s="190"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -7740,7 +7815,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="180"/>
+      <c r="A12" s="190"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -7758,7 +7833,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="180"/>
+      <c r="A13" s="190"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -7794,7 +7869,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -7838,7 +7913,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -7881,7 +7956,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -7924,7 +7999,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -7967,7 +8042,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8010,7 +8085,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -8053,7 +8128,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -8097,7 +8172,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -8140,7 +8215,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -8183,7 +8258,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -8225,7 +8300,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="181"/>
+      <c r="A25" s="191"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -8268,7 +8343,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="181"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -8296,30 +8371,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="177" t="s">
+      <c r="H28" s="187" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="178"/>
+      <c r="I28" s="188"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29980000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="177" t="s">
+      <c r="H29" s="187" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="178"/>
+      <c r="I29" s="188"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17988000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="177" t="s">
+      <c r="H30" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="178"/>
+      <c r="I30" s="188"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>17996000</v>
@@ -8396,18 +8471,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -8501,7 +8576,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="189" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -8547,7 +8622,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="180"/>
+      <c r="A8" s="190"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -8592,7 +8667,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="180"/>
+      <c r="A9" s="190"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -8631,7 +8706,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="180"/>
+      <c r="A10" s="190"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -8674,7 +8749,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="180"/>
+      <c r="A11" s="190"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -8719,7 +8794,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="180"/>
+      <c r="A12" s="190"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -8737,7 +8812,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="180"/>
+      <c r="A13" s="190"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -8773,7 +8848,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -8817,7 +8892,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -8860,7 +8935,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -8903,7 +8978,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -8946,7 +9021,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8989,7 +9064,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -9032,7 +9107,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -9075,7 +9150,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -9118,7 +9193,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -9161,7 +9236,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -9204,7 +9279,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="181"/>
+      <c r="A25" s="191"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -9247,7 +9322,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="181"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -9283,30 +9358,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="177" t="s">
+      <c r="H28" s="187" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="178"/>
+      <c r="I28" s="188"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31650000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="177" t="s">
+      <c r="H29" s="187" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="178"/>
+      <c r="I29" s="188"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18990000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="177" t="s">
+      <c r="H30" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="178"/>
+      <c r="I30" s="188"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>18990000</v>
@@ -9384,18 +9459,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -9489,7 +9564,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="179" t="s">
+      <c r="A7" s="189" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -9535,7 +9610,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="180"/>
+      <c r="A8" s="190"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -9580,7 +9655,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="180"/>
+      <c r="A9" s="190"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -9619,7 +9694,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="180"/>
+      <c r="A10" s="190"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -9662,7 +9737,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="180"/>
+      <c r="A11" s="190"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -9705,7 +9780,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="180"/>
+      <c r="A12" s="190"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -9723,7 +9798,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="180"/>
+      <c r="A13" s="190"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -9759,7 +9834,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="181" t="s">
+      <c r="A15" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -9802,7 +9877,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -9845,7 +9920,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -9888,7 +9963,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -9931,7 +10006,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -9974,7 +10049,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -10017,7 +10092,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -10062,7 +10137,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -10104,7 +10179,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -10147,7 +10222,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -10190,7 +10265,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="181"/>
+      <c r="A25" s="191"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -10233,7 +10308,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="181"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -10277,30 +10352,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="177" t="s">
+      <c r="H28" s="187" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="178"/>
+      <c r="I28" s="188"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29362000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="177" t="s">
+      <c r="H29" s="187" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="178"/>
+      <c r="I29" s="188"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17617200</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="177" t="s">
+      <c r="H30" s="187" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="178"/>
+      <c r="I30" s="188"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17619000</v>
@@ -10381,18 +10456,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -10486,7 +10561,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -10532,7 +10607,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -10579,7 +10654,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -10606,7 +10681,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -10646,17 +10721,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>28468000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -10696,9 +10771,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -10716,17 +10791,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>17080800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -10767,12 +10842,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -10812,12 +10887,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -10857,17 +10932,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>16486200</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -10910,7 +10985,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -10953,7 +11028,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -10996,7 +11071,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -11029,7 +11104,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -11072,7 +11147,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -11115,7 +11190,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -11157,7 +11232,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -11200,7 +11275,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -11256,7 +11331,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -11295,7 +11370,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -11334,7 +11409,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -11353,7 +11428,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -11372,7 +11447,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -11470,18 +11545,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -11575,7 +11650,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -11621,7 +11696,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -11664,7 +11739,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -11707,7 +11782,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11747,23 +11822,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>20755000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -11781,17 +11856,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>12453000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -11832,12 +11907,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -11877,12 +11952,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -11922,17 +11997,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>12451000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -11971,7 +12046,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -12014,7 +12089,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -12057,7 +12132,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -12100,7 +12175,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -12142,7 +12217,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -12185,7 +12260,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -12224,7 +12299,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -12245,7 +12320,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -12284,7 +12359,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -12321,7 +12396,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -12358,7 +12433,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -12391,7 +12466,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -12410,7 +12485,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -12509,18 +12584,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -12614,7 +12689,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -12660,7 +12735,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -12704,7 +12779,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -12747,7 +12822,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12787,23 +12862,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>29815000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -12821,17 +12896,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>17889000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -12872,12 +12947,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -12895,12 +12970,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -12940,17 +13015,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17728000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -12993,7 +13068,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -13036,7 +13111,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -13079,7 +13154,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -13122,7 +13197,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -13165,7 +13240,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -13208,7 +13283,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -13247,7 +13322,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -13268,7 +13343,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -13307,7 +13382,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -13344,7 +13419,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -13381,7 +13456,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -13416,7 +13491,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -13457,7 +13532,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -13558,18 +13633,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -13662,7 +13737,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -13708,7 +13783,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -13752,7 +13827,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -13795,7 +13870,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -13835,17 +13910,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>29241000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -13853,9 +13928,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -13873,17 +13948,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>17544600</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -13924,12 +13999,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -13947,12 +14022,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -13992,17 +14067,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17384600</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -14045,7 +14120,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -14088,7 +14163,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -14131,7 +14206,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -14174,7 +14249,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -14217,7 +14292,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -14260,7 +14335,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -14299,7 +14374,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -14320,7 +14395,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -14359,7 +14434,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -14397,7 +14472,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -14434,7 +14509,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -14468,7 +14543,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -14509,7 +14584,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -14581,32 +14656,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -15177,20 +15252,20 @@
       <c r="F25" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="176" t="s">
+      <c r="H25" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="176"/>
+      <c r="I25" s="186"/>
       <c r="J25" s="9">
         <f>SUM(H7:H1000)</f>
         <v>24820000</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(I7:I1000)</f>
         <v>14390000</v>
@@ -15333,18 +15408,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -15437,7 +15512,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -15485,7 +15560,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -15531,7 +15606,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -15574,7 +15649,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -15614,17 +15689,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>39465000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -15632,9 +15707,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -15652,17 +15727,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>23679000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -15703,12 +15778,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -15729,12 +15804,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -15774,17 +15849,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>23501000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -15827,7 +15902,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -15870,7 +15945,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -15913,7 +15988,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -15956,7 +16031,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -15999,7 +16074,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -16042,7 +16117,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16081,7 +16156,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -16102,7 +16177,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -16141,7 +16216,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -16179,7 +16254,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -16216,7 +16291,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -16251,7 +16326,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -16293,7 +16368,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -16393,18 +16468,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -16497,7 +16572,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -16543,7 +16618,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -16589,7 +16664,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -16632,7 +16707,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16672,17 +16747,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>28993000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -16690,9 +16765,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -16710,17 +16785,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>17395800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="181" t="s">
+      <c r="A13" s="191" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -16761,12 +16836,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
+      <c r="A14" s="191"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -16787,12 +16862,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="181"/>
+      <c r="A15" s="191"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -16832,17 +16907,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17285000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="181"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -16885,7 +16960,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="181"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -16930,7 +17005,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -16973,7 +17048,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -17016,7 +17091,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -17059,7 +17134,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="181"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -17102,7 +17177,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="181"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17141,7 +17216,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="181"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -17162,7 +17237,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="181"/>
+      <c r="A24" s="191"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -17201,7 +17276,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="182" t="s">
+      <c r="A26" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -17239,7 +17314,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="183"/>
+      <c r="A27" s="193"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -17276,7 +17351,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="183"/>
+      <c r="A28" s="193"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -17311,7 +17386,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="183"/>
+      <c r="A29" s="193"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -17352,7 +17427,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="183"/>
+      <c r="A30" s="193"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -17452,18 +17527,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -17556,7 +17631,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -17602,7 +17677,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -17648,7 +17723,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -17691,7 +17766,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -17731,17 +17806,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>23968000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -17749,9 +17824,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -17769,17 +17844,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>14380800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -17822,12 +17897,12 @@
       </c>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -17868,12 +17943,12 @@
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -17913,17 +17988,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14555400</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -17966,7 +18041,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -18005,7 +18080,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -18048,7 +18123,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -18091,7 +18166,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -18134,7 +18209,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -18173,7 +18248,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -18194,7 +18269,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -18215,7 +18290,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -18236,7 +18311,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -18257,7 +18332,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -18295,7 +18370,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -18332,7 +18407,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -18367,7 +18442,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -18408,7 +18483,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -18507,18 +18582,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -18611,7 +18686,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -18653,7 +18728,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -18699,7 +18774,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -18742,7 +18817,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -18782,17 +18857,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>25750000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -18800,9 +18875,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -18820,17 +18895,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>15450000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -18871,12 +18946,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -18916,12 +18991,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -18961,17 +19036,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>15330000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -18992,7 +19067,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -19035,7 +19110,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -19078,7 +19153,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -19121,7 +19196,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -19164,7 +19239,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -19203,7 +19278,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -19224,7 +19299,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -19261,7 +19336,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -19298,7 +19373,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -19335,7 +19410,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -19377,7 +19452,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -19400,7 +19475,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -19419,7 +19494,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -19438,7 +19513,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -19537,18 +19612,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -19641,7 +19716,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -19687,7 +19762,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -19733,7 +19808,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -19776,7 +19851,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -19816,17 +19891,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="190" t="s">
+      <c r="P10" s="200" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="190"/>
-      <c r="R10" s="185">
+      <c r="Q10" s="200"/>
+      <c r="R10" s="195">
         <f>SUM(H7:H999)</f>
         <v>24922000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -19834,9 +19909,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="190"/>
-      <c r="Q11" s="190"/>
-      <c r="R11" s="185"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="200"/>
+      <c r="R11" s="195"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -19854,17 +19929,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="184" t="s">
+      <c r="P12" s="194" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185">
+      <c r="Q12" s="194"/>
+      <c r="R12" s="195">
         <f>SUM(I7:I999)</f>
         <v>14953200</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -19905,12 +19980,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="184"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
+      <c r="P13" s="194"/>
+      <c r="Q13" s="194"/>
+      <c r="R13" s="195"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -19950,12 +20025,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
+      <c r="P14" s="194"/>
+      <c r="Q14" s="194"/>
+      <c r="R14" s="195"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -19995,17 +20070,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="186" t="s">
+      <c r="P15" s="196" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="186"/>
+      <c r="Q15" s="196"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14843000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -20026,7 +20101,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -20069,7 +20144,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -20114,7 +20189,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -20159,7 +20234,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -20202,7 +20277,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -20241,7 +20316,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -20262,7 +20337,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -20301,7 +20376,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -20340,7 +20415,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -20377,7 +20452,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -20420,7 +20495,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -20443,7 +20518,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -20462,7 +20537,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -20481,7 +20556,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -20556,18 +20631,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -20627,7 +20702,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -20672,7 +20747,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -20718,7 +20793,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="1">B8+1</f>
         <v>3</v>
@@ -20759,7 +20834,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -20798,26 +20873,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="193" t="s">
+      <c r="P10" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="193"/>
-      <c r="R10" s="194">
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
         <f>SUM(H7:H999)</f>
         <v>21305000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="193"/>
-      <c r="Q11" s="193"/>
-      <c r="R11" s="194"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -20834,17 +20909,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="195" t="s">
+      <c r="P12" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="195"/>
-      <c r="R12" s="194">
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
         <f>SUM(I7:I999)</f>
         <v>12783000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -20884,12 +20959,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="195"/>
-      <c r="Q13" s="195"/>
-      <c r="R13" s="194"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -20928,12 +21003,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="194"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="3">B14+1</f>
         <v>3</v>
@@ -20972,17 +21047,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="206"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12675000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -21004,7 +21079,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -21045,7 +21120,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -21092,7 +21167,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -21141,7 +21216,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -21182,7 +21257,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -21219,7 +21294,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -21241,7 +21316,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -21268,7 +21343,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -21295,7 +21370,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -21330,7 +21405,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -21371,7 +21446,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -21392,7 +21467,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -21411,7 +21486,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -21430,7 +21505,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -21495,18 +21570,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -21566,7 +21641,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -21611,7 +21686,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -21655,7 +21730,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -21696,7 +21771,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -21735,26 +21810,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="193" t="s">
+      <c r="P10" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="193"/>
-      <c r="R10" s="194">
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
         <f>SUM(H7:H999)</f>
         <v>25660000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="193"/>
-      <c r="Q11" s="193"/>
-      <c r="R11" s="194"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -21771,17 +21846,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="195" t="s">
+      <c r="P12" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="195"/>
-      <c r="R12" s="194">
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
         <f>SUM(I7:I999)</f>
         <v>13375000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -21821,12 +21896,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="195"/>
-      <c r="Q13" s="195"/>
-      <c r="R13" s="194"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -21865,12 +21940,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="194"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -21909,17 +21984,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="206"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13500000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -21944,7 +22019,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -21985,7 +22060,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -22037,7 +22112,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -22089,7 +22164,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -22130,7 +22205,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -22167,7 +22242,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -22192,7 +22267,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -22219,7 +22294,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -22246,7 +22321,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -22281,7 +22356,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -22322,7 +22397,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -22346,7 +22421,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -22365,7 +22440,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -22384,7 +22459,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -22449,18 +22524,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -22520,7 +22595,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -22567,7 +22642,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -22611,7 +22686,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -22652,7 +22727,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -22691,26 +22766,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="193" t="s">
+      <c r="P10" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="193"/>
-      <c r="R10" s="194">
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
         <f>SUM(H7:H999)</f>
         <v>25245000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="193"/>
-      <c r="Q11" s="193"/>
-      <c r="R11" s="194"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -22727,17 +22802,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="195" t="s">
+      <c r="P12" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="195"/>
-      <c r="R12" s="194">
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
         <f>SUM(I7:I999)</f>
         <v>13121500</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -22777,12 +22852,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="195"/>
-      <c r="Q13" s="195"/>
-      <c r="R13" s="194"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -22821,12 +22896,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="194"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -22865,17 +22940,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="206"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13128000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -22900,7 +22975,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -22941,7 +23016,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -22987,7 +23062,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -23037,7 +23112,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -23078,7 +23153,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -23115,7 +23190,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -23140,7 +23215,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -23167,7 +23242,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -23194,7 +23269,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -23229,7 +23304,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -23270,7 +23345,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -23294,7 +23369,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -23313,7 +23388,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -23332,7 +23407,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -23397,18 +23472,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -23468,7 +23543,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -23515,7 +23590,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
+      <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -23561,7 +23636,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
+      <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -23604,7 +23679,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
+      <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -23643,26 +23718,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="193" t="s">
+      <c r="P10" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="193"/>
-      <c r="R10" s="194">
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
         <f>SUM(H7:H999)</f>
         <v>22790000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="189"/>
+      <c r="A11" s="199"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="193"/>
-      <c r="Q11" s="193"/>
-      <c r="R11" s="194"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -23679,17 +23754,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="195" t="s">
+      <c r="P12" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="195"/>
-      <c r="R12" s="194">
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
         <f>SUM(I7:I999)</f>
         <v>12103000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -23729,12 +23804,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="195"/>
-      <c r="Q13" s="195"/>
-      <c r="R13" s="194"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="192"/>
+      <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -23773,12 +23848,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="195"/>
-      <c r="Q14" s="195"/>
-      <c r="R14" s="194"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="192"/>
+      <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -23817,17 +23892,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="206"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12000000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="192"/>
+      <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -23852,7 +23927,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="192"/>
+      <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -23893,7 +23968,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192"/>
+      <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -23939,7 +24014,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="192"/>
+      <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -23989,7 +24064,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="192"/>
+      <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -24030,7 +24105,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="192"/>
+      <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -24067,7 +24142,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="192"/>
+      <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -24092,7 +24167,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="192"/>
+      <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -24119,7 +24194,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="192"/>
+      <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -24146,7 +24221,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="192"/>
+      <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -24181,7 +24256,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192"/>
+      <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -24222,7 +24297,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="192"/>
+      <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -24246,7 +24321,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="192"/>
+      <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -24265,7 +24340,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="192"/>
+      <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -24284,9 +24359,954 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="192"/>
+      <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+    </row>
+    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="P12:Q14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="A13:A30"/>
+    <mergeCell ref="P15:Q15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3A04A6-898E-4DE4-9643-262E8A2E287A}">
+  <dimension ref="A3:S39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="35.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="19.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="37" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="183" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
+    </row>
+    <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="H4" s="116" t="s">
+        <v>190</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+    </row>
+    <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="158" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="158" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="158" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="158" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="197" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="67">
+        <v>91203011680</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="68">
+        <v>1450000</v>
+      </c>
+      <c r="I7" s="68">
+        <f>IF(H7="",0,IF(H7&gt;=1700000,H7*Q$19,H7*Q$18))</f>
+        <v>870000</v>
+      </c>
+      <c r="J7" s="68">
+        <v>870000</v>
+      </c>
+      <c r="K7" s="68">
+        <f>I7-J7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="136"/>
+      <c r="N7" s="76"/>
+      <c r="P7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="198"/>
+      <c r="B8" s="64">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="75">
+        <v>42094001136</v>
+      </c>
+      <c r="F8" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68">
+        <f t="shared" ref="I8:I10" si="0">IF(H8="",0,IF(H8&gt;=1700000,H8*Q$19,H8*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68">
+        <f t="shared" ref="K8:K10" si="1">I8-J8</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="69"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="P8" s="82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="198"/>
+      <c r="B9" s="64">
+        <f t="shared" ref="B9:B10" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="66">
+        <v>70081001153</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="68">
+        <v>700000</v>
+      </c>
+      <c r="I9" s="68">
+        <f t="shared" si="0"/>
+        <v>420000</v>
+      </c>
+      <c r="J9" s="74">
+        <v>350000</v>
+      </c>
+      <c r="K9" s="68">
+        <v>0</v>
+      </c>
+      <c r="L9" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="N9" s="79"/>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="198"/>
+      <c r="B10" s="64">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="73">
+        <v>27068001194</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="74">
+        <v>1400000</v>
+      </c>
+      <c r="I10" s="68">
+        <f t="shared" si="0"/>
+        <v>840000</v>
+      </c>
+      <c r="J10" s="74">
+        <v>840000</v>
+      </c>
+      <c r="K10" s="68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="76" t="s">
+        <v>192</v>
+      </c>
+      <c r="N10" s="76"/>
+      <c r="P10" s="203" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
+        <f>SUM(H7:H999)</f>
+        <v>18585000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="199"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="107"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="P12" s="205" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
+        <f>SUM(I7:I999)</f>
+        <v>10091000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="201" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="67">
+        <v>38096003688</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="68">
+        <v>2530000</v>
+      </c>
+      <c r="I13" s="68">
+        <f>IF(H13="",0,IF(H13&gt;=1700000,H13*Q$19,H13*Q$18))</f>
+        <v>1265000</v>
+      </c>
+      <c r="J13" s="68">
+        <v>1265000</v>
+      </c>
+      <c r="K13" s="68">
+        <f t="shared" ref="K13:K26" si="3">I13-J13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="202"/>
+      <c r="B14" s="64">
+        <f>B13+1</f>
+        <v>2</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="72">
+        <v>89099008054</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="74">
+        <v>1410000</v>
+      </c>
+      <c r="I14" s="68">
+        <f t="shared" ref="I14:I20" si="4">IF(H14="",0,IF(H14&gt;=1700000,H14*Q$19,H14*Q$18))</f>
+        <v>846000</v>
+      </c>
+      <c r="J14" s="74">
+        <v>846000</v>
+      </c>
+      <c r="K14" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
+    </row>
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="202"/>
+      <c r="B15" s="64">
+        <f t="shared" ref="B15:B30" si="5">B14+1</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="75">
+        <v>42088019031</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="68">
+        <v>1280000</v>
+      </c>
+      <c r="I15" s="68">
+        <f t="shared" si="4"/>
+        <v>768000</v>
+      </c>
+      <c r="J15" s="74">
+        <v>768000</v>
+      </c>
+      <c r="K15" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="174" t="s">
+        <v>191</v>
+      </c>
+      <c r="N15" s="85"/>
+      <c r="P15" s="206" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="160">
+        <f>SUM(J7:J98)</f>
+        <v>10021000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="202"/>
+      <c r="B16" s="64">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68">
+        <f>IF(H16="",0,IF(H16&gt;=1700000,H16*Q$19,H16*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="69"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+    </row>
+    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="202"/>
+      <c r="B17" s="64">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="75">
+        <v>95095009661</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="68">
+        <v>1155000</v>
+      </c>
+      <c r="I17" s="68">
+        <f t="shared" si="4"/>
+        <v>693000</v>
+      </c>
+      <c r="J17" s="74">
+        <v>693000</v>
+      </c>
+      <c r="K17" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="80"/>
+      <c r="N17" s="85"/>
+    </row>
+    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="202"/>
+      <c r="B18" s="64">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="81">
+        <v>91085001515</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68">
+        <f>IF(H18="",0,IF(H18&gt;=1700000,H18*Q$19,H18*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="74"/>
+      <c r="K18" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="131"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="P18" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="162">
+        <v>0.6</v>
+      </c>
+      <c r="S18" s="164" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="202"/>
+      <c r="B19" s="64">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="68">
+        <v>1700000</v>
+      </c>
+      <c r="I19" s="68">
+        <f t="shared" si="4"/>
+        <v>850000</v>
+      </c>
+      <c r="J19" s="68">
+        <v>850000</v>
+      </c>
+      <c r="K19" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" s="174" t="s">
+        <v>191</v>
+      </c>
+      <c r="N19" s="76"/>
+      <c r="P19" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="164" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="202"/>
+      <c r="B20" s="64">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="74">
+        <v>590000</v>
+      </c>
+      <c r="I20" s="68">
+        <f t="shared" si="4"/>
+        <v>354000</v>
+      </c>
+      <c r="J20" s="68">
+        <v>354000</v>
+      </c>
+      <c r="K20" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="79"/>
+      <c r="N20" s="76"/>
+    </row>
+    <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="202"/>
+      <c r="B21" s="64">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C21" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="177"/>
+      <c r="G21" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="74">
+        <v>2080000</v>
+      </c>
+      <c r="I21" s="68">
+        <f>IF(H21="",0,IF(H21&gt;=1700000,H21*Q$19,H21*Q$18))</f>
+        <v>1040000</v>
+      </c>
+      <c r="J21" s="74">
+        <v>1040000</v>
+      </c>
+      <c r="K21" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M21" s="173"/>
+      <c r="N21" s="76"/>
+    </row>
+    <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="202"/>
+      <c r="B22" s="64">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="177"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="68">
+        <f>IF(H22="",0,IF(H22&gt;=1700000,H22*Q$19,H22*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="177"/>
+      <c r="K22" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="177"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+    </row>
+    <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="202"/>
+      <c r="B23" s="64">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="133"/>
+      <c r="I23" s="68">
+        <f t="shared" ref="I23:I26" si="6">IF(H23="",0,IF(H23&gt;=1700000,H23*Q$19,H23*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="132"/>
+      <c r="K23" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="69"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="79"/>
+    </row>
+    <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="202"/>
+      <c r="B24" s="64">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="133"/>
+      <c r="I24" s="68">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="133"/>
+      <c r="K24" s="68">
+        <f>I24-J24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="69"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+    </row>
+    <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="202"/>
+      <c r="B25" s="64">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="68">
+        <v>2100000</v>
+      </c>
+      <c r="I25" s="68">
+        <f>IF(H25="",0,IF(H25&gt;=1700000,H25*Q$19,H25*Q$18))</f>
+        <v>1050000</v>
+      </c>
+      <c r="J25" s="68">
+        <v>1050000</v>
+      </c>
+      <c r="K25" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+    </row>
+    <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="202"/>
+      <c r="B26" s="64">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="67">
+        <v>89078016404</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="179">
+        <v>2190000</v>
+      </c>
+      <c r="I26" s="68">
+        <f t="shared" si="6"/>
+        <v>1095000</v>
+      </c>
+      <c r="J26" s="133">
+        <v>1095000</v>
+      </c>
+      <c r="K26" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M26" s="136"/>
+      <c r="N26" s="76"/>
+    </row>
+    <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="202"/>
+      <c r="B27" s="64">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C27" s="177"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="177"/>
+      <c r="F27" s="177"/>
+      <c r="G27" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="177"/>
+      <c r="I27" s="68">
+        <f>IF(H27="",0,IF(H27&gt;=1700000,H27*Q$19,H27*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="177"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="76"/>
+    </row>
+    <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="202"/>
+      <c r="B28" s="64">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="79"/>
+    </row>
+    <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="202"/>
+      <c r="B29" s="64">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+    </row>
+    <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="202"/>
+      <c r="B30" s="64">
+        <f t="shared" si="5"/>
         <v>18</v>
       </c>
       <c r="C30" s="71"/>
@@ -24346,32 +25366,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -25040,20 +26060,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29135000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17346000</v>
@@ -25149,6 +26169,1854 @@
   <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98EFEDE5-2874-4668-9159-27236F693D65}">
+  <dimension ref="A3:S39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="35.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="19.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="37" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="183" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
+    </row>
+    <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="H4" s="116" t="s">
+        <v>197</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+    </row>
+    <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="158" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="158" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="158" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="158" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="197" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="67">
+        <v>91203011680</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="68">
+        <v>1400000</v>
+      </c>
+      <c r="I7" s="68">
+        <f>IF(H7="",0,IF(H7&gt;=1700000,H7*Q$19,H7*Q$18))</f>
+        <v>840000</v>
+      </c>
+      <c r="J7" s="68">
+        <v>840000</v>
+      </c>
+      <c r="K7" s="68">
+        <f>I7-J7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="136"/>
+      <c r="N7" s="76"/>
+      <c r="P7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="198"/>
+      <c r="B8" s="64">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="75">
+        <v>42094001136</v>
+      </c>
+      <c r="F8" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68">
+        <f t="shared" ref="I8:I10" si="0">IF(H8="",0,IF(H8&gt;=1700000,H8*Q$19,H8*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68">
+        <f t="shared" ref="K8:K10" si="1">I8-J8</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="69"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="P8" s="82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="198"/>
+      <c r="B9" s="64">
+        <f t="shared" ref="B9:B10" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="66">
+        <v>70081001153</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="68">
+        <v>1080000</v>
+      </c>
+      <c r="I9" s="68">
+        <f t="shared" si="0"/>
+        <v>648000</v>
+      </c>
+      <c r="J9" s="74">
+        <v>650000</v>
+      </c>
+      <c r="K9" s="68">
+        <v>0</v>
+      </c>
+      <c r="L9" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="76" t="s">
+        <v>198</v>
+      </c>
+      <c r="N9" s="79"/>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="198"/>
+      <c r="B10" s="64">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="73">
+        <v>27068001194</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="74">
+        <v>1150000</v>
+      </c>
+      <c r="I10" s="68">
+        <f t="shared" si="0"/>
+        <v>690000</v>
+      </c>
+      <c r="J10" s="74">
+        <v>690000</v>
+      </c>
+      <c r="K10" s="68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="P10" s="203" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
+        <f>SUM(H7:H999)</f>
+        <v>18425000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="199"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="107"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="P12" s="205" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
+        <f>SUM(I7:I999)</f>
+        <v>10290500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="201" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="67">
+        <v>38096003688</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="68">
+        <v>1300000</v>
+      </c>
+      <c r="I13" s="68">
+        <f>IF(H13="",0,IF(H13&gt;=1700000,H13*Q$19,H13*Q$18))</f>
+        <v>780000</v>
+      </c>
+      <c r="J13" s="68">
+        <v>780000</v>
+      </c>
+      <c r="K13" s="68">
+        <f t="shared" ref="K13:K26" si="3">I13-J13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="202"/>
+      <c r="B14" s="64">
+        <f>B13+1</f>
+        <v>2</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="72">
+        <v>89099008054</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="74">
+        <v>1050000</v>
+      </c>
+      <c r="I14" s="68">
+        <f t="shared" ref="I14:I20" si="4">IF(H14="",0,IF(H14&gt;=1700000,H14*Q$19,H14*Q$18))</f>
+        <v>630000</v>
+      </c>
+      <c r="J14" s="74">
+        <v>630000</v>
+      </c>
+      <c r="K14" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
+    </row>
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="202"/>
+      <c r="B15" s="64">
+        <f t="shared" ref="B15:B30" si="5">B14+1</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="75">
+        <v>42088019031</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="68">
+        <v>1410000</v>
+      </c>
+      <c r="I15" s="68">
+        <f t="shared" si="4"/>
+        <v>846000</v>
+      </c>
+      <c r="J15" s="74">
+        <v>846000</v>
+      </c>
+      <c r="K15" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="76"/>
+      <c r="N15" s="85"/>
+      <c r="P15" s="206" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="160">
+        <f>SUM(J7:J98)</f>
+        <v>10183000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="202"/>
+      <c r="B16" s="64">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68">
+        <f>IF(H16="",0,IF(H16&gt;=1700000,H16*Q$19,H16*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="69"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+    </row>
+    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="202"/>
+      <c r="B17" s="64">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="75">
+        <v>95095009661</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="68">
+        <v>850000</v>
+      </c>
+      <c r="I17" s="68">
+        <f t="shared" si="4"/>
+        <v>510000</v>
+      </c>
+      <c r="J17" s="74">
+        <v>510000</v>
+      </c>
+      <c r="K17" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="80"/>
+      <c r="N17" s="85"/>
+    </row>
+    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="202"/>
+      <c r="B18" s="64">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="81">
+        <v>91085001515</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68">
+        <f>IF(H18="",0,IF(H18&gt;=1700000,H18*Q$19,H18*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="74"/>
+      <c r="K18" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="131"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="P18" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="162">
+        <v>0.6</v>
+      </c>
+      <c r="S18" s="164" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="202"/>
+      <c r="B19" s="64">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="68">
+        <v>1490000</v>
+      </c>
+      <c r="I19" s="68">
+        <f t="shared" si="4"/>
+        <v>894000</v>
+      </c>
+      <c r="J19" s="68">
+        <v>890000</v>
+      </c>
+      <c r="K19" s="68">
+        <f t="shared" si="3"/>
+        <v>4000</v>
+      </c>
+      <c r="L19" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="N19" s="76"/>
+      <c r="P19" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="164" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="202"/>
+      <c r="B20" s="64">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="74">
+        <v>2500000</v>
+      </c>
+      <c r="I20" s="68">
+        <f t="shared" si="4"/>
+        <v>1250000</v>
+      </c>
+      <c r="J20" s="68">
+        <v>1250000</v>
+      </c>
+      <c r="K20" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M20" s="79"/>
+      <c r="N20" s="76"/>
+    </row>
+    <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="202"/>
+      <c r="B21" s="64">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C21" s="180" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="169"/>
+      <c r="E21" s="169"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="181" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="144"/>
+      <c r="I21" s="143">
+        <f>IF(H21="",0,IF(H21&gt;=1700000,H21*Q$19,H21*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="144"/>
+      <c r="K21" s="143">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="150"/>
+      <c r="M21" s="182" t="s">
+        <v>194</v>
+      </c>
+      <c r="N21" s="76"/>
+    </row>
+    <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="202"/>
+      <c r="B22" s="64">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="177"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="68">
+        <f>IF(H22="",0,IF(H22&gt;=1700000,H22*Q$19,H22*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="177"/>
+      <c r="K22" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="177"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+    </row>
+    <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="202"/>
+      <c r="B23" s="64">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="133">
+        <v>1050000</v>
+      </c>
+      <c r="I23" s="68">
+        <f t="shared" ref="I23:I26" si="6">IF(H23="",0,IF(H23&gt;=1700000,H23*Q$19,H23*Q$18))</f>
+        <v>630000</v>
+      </c>
+      <c r="J23" s="132">
+        <v>525000</v>
+      </c>
+      <c r="K23" s="68">
+        <v>0</v>
+      </c>
+      <c r="L23" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M23" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="N23" s="79"/>
+    </row>
+    <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="202"/>
+      <c r="B24" s="64">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="133"/>
+      <c r="I24" s="68">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="133"/>
+      <c r="K24" s="68">
+        <f>I24-J24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="69"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+    </row>
+    <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="202"/>
+      <c r="B25" s="64">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="68">
+        <v>3435000</v>
+      </c>
+      <c r="I25" s="68">
+        <f>IF(H25="",0,IF(H25&gt;=1700000,H25*Q$19,H25*Q$18))</f>
+        <v>1717500</v>
+      </c>
+      <c r="J25" s="68">
+        <v>1717000</v>
+      </c>
+      <c r="K25" s="68">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="L25" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+    </row>
+    <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="202"/>
+      <c r="B26" s="64">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="67">
+        <v>89078016404</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="179">
+        <v>1710000</v>
+      </c>
+      <c r="I26" s="68">
+        <f t="shared" si="6"/>
+        <v>855000</v>
+      </c>
+      <c r="J26" s="133">
+        <v>855000</v>
+      </c>
+      <c r="K26" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="M26" s="136"/>
+      <c r="N26" s="76"/>
+    </row>
+    <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="202"/>
+      <c r="B27" s="64">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C27" s="177"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="177"/>
+      <c r="F27" s="177"/>
+      <c r="G27" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="177"/>
+      <c r="I27" s="68">
+        <f>IF(H27="",0,IF(H27&gt;=1700000,H27*Q$19,H27*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="177"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="76"/>
+    </row>
+    <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="202"/>
+      <c r="B28" s="64">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="79"/>
+    </row>
+    <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="202"/>
+      <c r="B29" s="64">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+    </row>
+    <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="202"/>
+      <c r="B30" s="64">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+    </row>
+    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="P12:Q14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="A13:A30"/>
+    <mergeCell ref="P15:Q15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6619632F-92FC-4DC6-B93E-FE9F60EBD745}">
+  <dimension ref="A3:S39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="35.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="19.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="37" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="183" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="183"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="183"/>
+      <c r="F3" s="183"/>
+      <c r="G3" s="183"/>
+      <c r="H3" s="183"/>
+      <c r="I3" s="183"/>
+      <c r="J3" s="183"/>
+      <c r="K3" s="183"/>
+    </row>
+    <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="H4" s="116" t="s">
+        <v>199</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+    </row>
+    <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="158" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="158" t="s">
+        <v>115</v>
+      </c>
+      <c r="K6" s="158" t="s">
+        <v>116</v>
+      </c>
+      <c r="L6" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="158" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="197" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="67">
+        <v>91203011680</v>
+      </c>
+      <c r="F7" s="66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68">
+        <f>IF(H7="",0,IF(H7&gt;=1700000,H7*Q$19,H7*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68">
+        <f>I7-J7</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M7" s="136"/>
+      <c r="N7" s="76"/>
+      <c r="P7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="198"/>
+      <c r="B8" s="64">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="75">
+        <v>42094001136</v>
+      </c>
+      <c r="F8" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="68">
+        <v>1000000</v>
+      </c>
+      <c r="I8" s="68">
+        <f t="shared" ref="I8:I10" si="0">IF(H8="",0,IF(H8&gt;=1700000,H8*Q$19,H8*Q$18))</f>
+        <v>600000</v>
+      </c>
+      <c r="J8" s="68">
+        <v>500000</v>
+      </c>
+      <c r="K8" s="68">
+        <f t="shared" ref="K8:K10" si="1">I8-J8</f>
+        <v>100000</v>
+      </c>
+      <c r="L8" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="76" t="s">
+        <v>201</v>
+      </c>
+      <c r="N8" s="76"/>
+      <c r="P8" s="82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="198"/>
+      <c r="B9" s="64">
+        <f t="shared" ref="B9:B10" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="66">
+        <v>70081001153</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="74"/>
+      <c r="K9" s="68">
+        <v>0</v>
+      </c>
+      <c r="L9" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M9" s="76"/>
+      <c r="N9" s="79"/>
+    </row>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="198"/>
+      <c r="B10" s="64">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="73">
+        <v>27068001194</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="74"/>
+      <c r="I10" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="74"/>
+      <c r="K10" s="68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="P10" s="203" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="203"/>
+      <c r="R10" s="204">
+        <f>SUM(H7:H999)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="199"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="176"/>
+      <c r="K11" s="176"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="203"/>
+      <c r="R11" s="204"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="107"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+      <c r="P12" s="205" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q12" s="205"/>
+      <c r="R12" s="204">
+        <f>SUM(I7:I999)</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="201" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="67">
+        <v>38096003688</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68">
+        <f>IF(H13="",0,IF(H13&gt;=1700000,H13*Q$19,H13*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68">
+        <f t="shared" ref="K13:K26" si="3">I13-J13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13" s="76"/>
+      <c r="N13" s="76"/>
+      <c r="P13" s="205"/>
+      <c r="Q13" s="205"/>
+      <c r="R13" s="204"/>
+    </row>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="202"/>
+      <c r="B14" s="64">
+        <f>B13+1</f>
+        <v>2</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="72">
+        <v>89099008054</v>
+      </c>
+      <c r="F14" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="74"/>
+      <c r="I14" s="68">
+        <f t="shared" ref="I14:I20" si="4">IF(H14="",0,IF(H14&gt;=1700000,H14*Q$19,H14*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="74"/>
+      <c r="K14" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="P14" s="205"/>
+      <c r="Q14" s="205"/>
+      <c r="R14" s="204"/>
+    </row>
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="202"/>
+      <c r="B15" s="64">
+        <f t="shared" ref="B15:B30" si="5">B14+1</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="75">
+        <v>42088019031</v>
+      </c>
+      <c r="F15" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="74"/>
+      <c r="K15" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M15" s="76"/>
+      <c r="N15" s="85"/>
+      <c r="P15" s="206" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="160">
+        <f>SUM(J7:J98)</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="202"/>
+      <c r="B16" s="64">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68">
+        <f>IF(H16="",0,IF(H16&gt;=1700000,H16*Q$19,H16*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="69"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+    </row>
+    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="202"/>
+      <c r="B17" s="64">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="75">
+        <v>95095009661</v>
+      </c>
+      <c r="F17" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="74"/>
+      <c r="K17" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="80"/>
+      <c r="N17" s="85"/>
+    </row>
+    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="202"/>
+      <c r="B18" s="64">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="81">
+        <v>91085001515</v>
+      </c>
+      <c r="F18" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68">
+        <f>IF(H18="",0,IF(H18&gt;=1700000,H18*Q$19,H18*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="74"/>
+      <c r="K18" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="131"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="76"/>
+      <c r="P18" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="162">
+        <v>0.6</v>
+      </c>
+      <c r="S18" s="164" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="202"/>
+      <c r="B19" s="64">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="76"/>
+      <c r="N19" s="76"/>
+      <c r="P19" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="164" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="202"/>
+      <c r="B20" s="64">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="74"/>
+      <c r="I20" s="68">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="79"/>
+      <c r="N20" s="76"/>
+    </row>
+    <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="202"/>
+      <c r="B21" s="64">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C21" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="177"/>
+      <c r="G21" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="74"/>
+      <c r="I21" s="68">
+        <f>IF(H21="",0,IF(H21&gt;=1700000,H21*Q$19,H21*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="74"/>
+      <c r="K21" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="173"/>
+      <c r="N21" s="76"/>
+    </row>
+    <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="202"/>
+      <c r="B22" s="64">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="177"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="68">
+        <f>IF(H22="",0,IF(H22&gt;=1700000,H22*Q$19,H22*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="177"/>
+      <c r="K22" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="177"/>
+      <c r="M22" s="105"/>
+      <c r="N22" s="105"/>
+    </row>
+    <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="202"/>
+      <c r="B23" s="64">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="133"/>
+      <c r="I23" s="68">
+        <f t="shared" ref="I23:I26" si="6">IF(H23="",0,IF(H23&gt;=1700000,H23*Q$19,H23*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="132"/>
+      <c r="K23" s="68">
+        <v>0</v>
+      </c>
+      <c r="L23" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="105"/>
+      <c r="N23" s="79"/>
+    </row>
+    <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="202"/>
+      <c r="B24" s="64">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="133"/>
+      <c r="I24" s="68">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="133"/>
+      <c r="K24" s="68">
+        <f>I24-J24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="69"/>
+      <c r="M24" s="105"/>
+      <c r="N24" s="105"/>
+    </row>
+    <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="202"/>
+      <c r="B25" s="64">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="75" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68">
+        <f>IF(H25="",0,IF(H25&gt;=1700000,H25*Q$19,H25*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="68"/>
+      <c r="K25" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+    </row>
+    <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="202"/>
+      <c r="B26" s="64">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="67">
+        <v>89078016404</v>
+      </c>
+      <c r="F26" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="179"/>
+      <c r="I26" s="68">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="133"/>
+      <c r="K26" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="136"/>
+      <c r="N26" s="76"/>
+    </row>
+    <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="202"/>
+      <c r="B27" s="64">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C27" s="177"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="177"/>
+      <c r="F27" s="177"/>
+      <c r="G27" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="H27" s="177"/>
+      <c r="I27" s="68">
+        <f>IF(H27="",0,IF(H27&gt;=1700000,H27*Q$19,H27*Q$18))</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="177"/>
+      <c r="K27" s="177"/>
+      <c r="L27" s="177"/>
+      <c r="M27" s="136"/>
+      <c r="N27" s="76"/>
+    </row>
+    <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="202"/>
+      <c r="B28" s="64">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="105"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="79"/>
+    </row>
+    <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="202"/>
+      <c r="B29" s="64">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="76"/>
+      <c r="N29" s="76"/>
+    </row>
+    <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="202"/>
+      <c r="B30" s="64">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="132"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+    </row>
+    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="P12:Q14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="A13:A30"/>
+    <mergeCell ref="P15:Q15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -25175,32 +28043,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -25865,20 +28733,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32170000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19075000</v>
@@ -25999,32 +28867,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -26676,20 +29544,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30806000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18342000</v>
@@ -26810,32 +29678,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -27482,20 +30350,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30762000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18280000</v>
@@ -27619,32 +30487,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -28297,20 +31165,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31566000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18200000</v>
@@ -28434,32 +31302,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -29109,20 +31977,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18612000</v>
@@ -29248,32 +32116,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
+      <c r="C2" s="183"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="183"/>
+      <c r="F2" s="183"/>
+      <c r="G2" s="183"/>
+      <c r="H2" s="183"/>
+      <c r="I2" s="183"/>
+      <c r="J2" s="183"/>
+      <c r="K2" s="183"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="184" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
+      <c r="C3" s="185"/>
+      <c r="D3" s="185"/>
+      <c r="E3" s="185"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -29935,20 +32803,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="176" t="s">
+      <c r="H26" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="176"/>
+      <c r="I26" s="186"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32130000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="176" t="s">
+      <c r="H27" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="176"/>
+      <c r="I27" s="186"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19110000</v>

--- a/Theo dõi/T1 2026 02-01.xlsx
+++ b/Theo dõi/T1 2026 02-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DE3FD2-0981-41AC-B839-3CE30A0D846F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA166D2-2BC8-4751-BC62-86E471F35EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="16" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3440" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="205">
   <si>
     <t>STT</t>
   </si>
@@ -672,6 +672,15 @@
   </si>
   <si>
     <t>5 5 thọt 100</t>
+  </si>
+  <si>
+    <t>thọt 5k</t>
+  </si>
+  <si>
+    <t>HUỲNH VIỆT CHƯƠNG</t>
+  </si>
+  <si>
+    <t>TRƯƠNG THANH TÚ</t>
   </si>
 </sst>
 </file>
@@ -27120,15 +27129,15 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6619632F-92FC-4DC6-B93E-FE9F60EBD745}">
-  <dimension ref="A3:S39"/>
+  <dimension ref="A3:Q39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="35.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
@@ -27143,7 +27152,7 @@
     <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="B3" s="183" t="s">
         <v>31</v>
       </c>
@@ -27157,7 +27166,7 @@
       <c r="J3" s="183"/>
       <c r="K3" s="183"/>
     </row>
-    <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
       <c r="E4" s="117"/>
@@ -27168,8 +27177,8 @@
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
     </row>
-    <row r="5" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="105"/>
       <c r="B6" s="158" t="s">
         <v>0</v>
@@ -27181,40 +27190,34 @@
         <v>50</v>
       </c>
       <c r="E6" s="158" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="F6" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="158" t="s">
-        <v>49</v>
+        <v>4</v>
+      </c>
+      <c r="G6" s="159" t="s">
+        <v>142</v>
       </c>
       <c r="H6" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="159" t="s">
-        <v>142</v>
+        <v>115</v>
+      </c>
+      <c r="I6" s="158" t="s">
+        <v>116</v>
       </c>
       <c r="J6" s="158" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="K6" s="158" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="L6" s="158" t="s">
-        <v>7</v>
-      </c>
-      <c r="M6" s="158" t="s">
-        <v>34</v>
-      </c>
-      <c r="N6" s="158" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="87" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="197" t="s">
         <v>119</v>
       </c>
@@ -27224,38 +27227,34 @@
       <c r="C7" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="67">
-        <v>91203011680</v>
-      </c>
-      <c r="F7" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="66" t="s">
+      <c r="D7" s="66"/>
+      <c r="E7" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="68"/>
+      <c r="F7" s="68">
+        <v>1700000</v>
+      </c>
+      <c r="G7" s="68">
+        <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
+        <v>1020000</v>
+      </c>
+      <c r="H7" s="68">
+        <v>1020000</v>
+      </c>
       <c r="I7" s="68">
-        <f>IF(H7="",0,IF(H7&gt;=1700000,H7*Q$19,H7*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68">
-        <f>I7-J7</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M7" s="136"/>
-      <c r="N7" s="76"/>
-      <c r="P7" s="88" t="s">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="88" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="136"/>
+      <c r="L7" s="76"/>
+      <c r="N7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="198"/>
       <c r="B8" s="64">
         <f>B7+1</f>
@@ -27264,44 +27263,36 @@
       <c r="C8" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="D8" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="75">
-        <v>42094001136</v>
-      </c>
-      <c r="F8" s="75" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="75" t="s">
+      <c r="D8" s="75"/>
+      <c r="E8" s="75" t="s">
         <v>36</v>
       </c>
+      <c r="F8" s="68">
+        <v>1000000</v>
+      </c>
+      <c r="G8" s="68">
+        <f t="shared" ref="G8:G10" si="0">IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
+        <v>600000</v>
+      </c>
       <c r="H8" s="68">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="I8" s="68">
-        <f t="shared" ref="I8:I10" si="0">IF(H8="",0,IF(H8&gt;=1700000,H8*Q$19,H8*Q$18))</f>
-        <v>600000</v>
-      </c>
-      <c r="J8" s="68">
-        <v>500000</v>
-      </c>
-      <c r="K8" s="68">
-        <f t="shared" ref="K8:K10" si="1">I8-J8</f>
+        <f t="shared" ref="I8:I10" si="1">G8-H8</f>
         <v>100000</v>
       </c>
-      <c r="L8" s="88" t="s">
+      <c r="J8" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="76" t="s">
+      <c r="K8" s="76" t="s">
         <v>201</v>
       </c>
-      <c r="N8" s="76"/>
-      <c r="P8" s="82" t="s">
+      <c r="L8" s="76"/>
+      <c r="N8" s="82" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="198"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
@@ -27310,34 +27301,30 @@
       <c r="C9" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="D9" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="66">
-        <v>70081001153</v>
-      </c>
-      <c r="F9" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="66" t="s">
+      <c r="D9" s="66"/>
+      <c r="E9" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="68"/>
+      <c r="F9" s="68">
+        <v>1540000</v>
+      </c>
+      <c r="G9" s="68">
+        <f t="shared" si="0"/>
+        <v>924000</v>
+      </c>
+      <c r="H9" s="74">
+        <v>920000</v>
+      </c>
       <c r="I9" s="68">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="74"/>
-      <c r="K9" s="68">
-        <v>0</v>
-      </c>
-      <c r="L9" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="76"/>
-      <c r="N9" s="79"/>
-    </row>
-    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="J9" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="76"/>
+      <c r="L9" s="79"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="198"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
@@ -27346,85 +27333,77 @@
       <c r="C10" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="73" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="73">
-        <v>27068001194</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>105</v>
-      </c>
-      <c r="G10" s="73" t="s">
+      <c r="D10" s="73"/>
+      <c r="E10" s="73" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="74"/>
+      <c r="F10" s="74">
+        <v>1600000</v>
+      </c>
+      <c r="G10" s="68">
+        <f t="shared" si="0"/>
+        <v>960000</v>
+      </c>
+      <c r="H10" s="74">
+        <v>960000</v>
+      </c>
       <c r="I10" s="68">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="74"/>
-      <c r="K10" s="68">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L10" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="76"/>
-      <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="J10" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="N10" s="203" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="O10" s="203"/>
+      <c r="P10" s="204">
         <f>SUM(H7:H999)</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>12810000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="199"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="175"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
       <c r="H11" s="176"/>
       <c r="I11" s="176"/>
-      <c r="J11" s="176"/>
-      <c r="K11" s="176"/>
-      <c r="L11" s="175"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
-    </row>
-    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="175"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="N11" s="203"/>
+      <c r="O11" s="203"/>
+      <c r="P11" s="204"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
       <c r="B12" s="89"/>
       <c r="C12" s="90"/>
       <c r="D12" s="89"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="N12" s="205" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="O12" s="205"/>
+      <c r="P12" s="204">
         <f>SUM(I7:I999)</f>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="201" t="s">
         <v>118</v>
       </c>
@@ -27434,38 +27413,36 @@
       <c r="C13" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="66" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="67">
-        <v>38096003688</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="66" t="s">
+      <c r="D13" s="66"/>
+      <c r="E13" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="68"/>
+      <c r="F13" s="68">
+        <v>2230000</v>
+      </c>
+      <c r="G13" s="68">
+        <f>IF(F13="",0,IF(F13&gt;=1700000,F13*O$19,F13*O$18))</f>
+        <v>1115000</v>
+      </c>
+      <c r="H13" s="68">
+        <v>1110000</v>
+      </c>
       <c r="I13" s="68">
-        <f>IF(H13="",0,IF(H13&gt;=1700000,H13*Q$19,H13*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68">
-        <f t="shared" ref="K13:K26" si="3">I13-J13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
-    </row>
-    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="I13:I27" si="3">G13-H13</f>
+        <v>5000</v>
+      </c>
+      <c r="J13" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="L13" s="76"/>
+      <c r="N13" s="205"/>
+      <c r="O13" s="205"/>
+      <c r="P13" s="204"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="202"/>
       <c r="B14" s="64">
         <f>B13+1</f>
@@ -27474,38 +27451,34 @@
       <c r="C14" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="72">
-        <v>89099008054</v>
-      </c>
-      <c r="F14" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="73" t="s">
+      <c r="D14" s="73"/>
+      <c r="E14" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="74"/>
+      <c r="F14" s="74">
+        <v>1967000</v>
+      </c>
+      <c r="G14" s="68">
+        <f t="shared" ref="G14:G20" si="4">IF(F14="",0,IF(F14&gt;=1700000,F14*O$19,F14*O$18))</f>
+        <v>983500</v>
+      </c>
+      <c r="H14" s="74">
+        <v>984000</v>
+      </c>
       <c r="I14" s="68">
-        <f t="shared" ref="I14:I20" si="4">IF(H14="",0,IF(H14&gt;=1700000,H14*Q$19,H14*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="74"/>
-      <c r="K14" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
-    </row>
-    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-500</v>
+      </c>
+      <c r="J14" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="N14" s="205"/>
+      <c r="O14" s="205"/>
+      <c r="P14" s="204"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="202"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
@@ -27514,43 +27487,39 @@
       <c r="C15" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="75">
-        <v>42088019031</v>
-      </c>
-      <c r="F15" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="75" t="s">
+      <c r="D15" s="75"/>
+      <c r="E15" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="68"/>
+      <c r="F15" s="68">
+        <v>1980000</v>
+      </c>
+      <c r="G15" s="68">
+        <f t="shared" si="4"/>
+        <v>990000</v>
+      </c>
+      <c r="H15" s="74">
+        <v>990000</v>
+      </c>
       <c r="I15" s="68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="74"/>
-      <c r="K15" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L15" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M15" s="76"/>
-      <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="J15" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="76"/>
+      <c r="L15" s="85"/>
+      <c r="N15" s="206" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
-      <c r="R15" s="160">
+      <c r="O15" s="206"/>
+      <c r="P15" s="160">
         <f>SUM(J7:J98)</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="202"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
@@ -27559,23 +27528,21 @@
       <c r="C16" s="77"/>
       <c r="D16" s="75"/>
       <c r="E16" s="75"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68">
+        <f>IF(F16="",0,IF(F16&gt;=1700000,F16*O$19,F16*O$18))</f>
+        <v>0</v>
+      </c>
       <c r="H16" s="68"/>
       <c r="I16" s="68">
-        <f>IF(H16="",0,IF(H16&gt;=1700000,H16*Q$19,H16*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L16" s="69"/>
-      <c r="M16" s="76"/>
-      <c r="N16" s="76"/>
-    </row>
-    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="69"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="202"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
@@ -27584,77 +27551,65 @@
       <c r="C17" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="75" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="75">
-        <v>95095009661</v>
-      </c>
-      <c r="F17" s="75" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="75" t="s">
+      <c r="D17" s="75"/>
+      <c r="E17" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="68"/>
+      <c r="F17" s="68">
+        <v>1700000</v>
+      </c>
+      <c r="G17" s="68">
+        <f t="shared" si="4"/>
+        <v>850000</v>
+      </c>
+      <c r="H17" s="74">
+        <v>850000</v>
+      </c>
       <c r="I17" s="68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="74"/>
-      <c r="K17" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L17" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M17" s="80"/>
-      <c r="N17" s="85"/>
-    </row>
-    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J17" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="80"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="202"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="C18" s="77"/>
-      <c r="D18" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="81">
-        <v>91085001515</v>
-      </c>
-      <c r="F18" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="75" t="s">
+      <c r="D18" s="75"/>
+      <c r="E18" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68">
+        <f>IF(F18="",0,IF(F18&gt;=1700000,F18*O$19,F18*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="74"/>
       <c r="I18" s="68">
-        <f>IF(H18="",0,IF(H18&gt;=1700000,H18*Q$19,H18*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="74"/>
-      <c r="K18" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L18" s="131"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="76"/>
-      <c r="P18" s="157" t="s">
+      <c r="J18" s="131"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="N18" s="157" t="s">
         <v>65</v>
       </c>
-      <c r="Q18" s="162">
+      <c r="O18" s="162">
         <v>0.6</v>
       </c>
-      <c r="S18" s="164" t="s">
+      <c r="Q18" s="164" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="202"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
@@ -27663,44 +27618,40 @@
       <c r="C19" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="64" t="s">
-        <v>54</v>
-      </c>
+      <c r="D19" s="64"/>
       <c r="E19" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="H19" s="68"/>
+      <c r="F19" s="68">
+        <v>1710000</v>
+      </c>
+      <c r="G19" s="68">
+        <f t="shared" si="4"/>
+        <v>855000</v>
+      </c>
+      <c r="H19" s="68">
+        <v>860000</v>
+      </c>
       <c r="I19" s="68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19" s="76"/>
-      <c r="N19" s="76"/>
-      <c r="P19" s="157" t="s">
+        <v>-5000</v>
+      </c>
+      <c r="J19" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="76"/>
+      <c r="L19" s="76"/>
+      <c r="N19" s="157" t="s">
         <v>65</v>
       </c>
-      <c r="Q19" s="163">
+      <c r="O19" s="163">
         <v>0.5</v>
       </c>
-      <c r="S19" s="164" t="s">
+      <c r="Q19" s="164" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="202"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
@@ -27709,66 +27660,64 @@
       <c r="C20" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="70" t="s">
-        <v>89</v>
-      </c>
-      <c r="F20" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="64" t="s">
+      <c r="D20" s="70"/>
+      <c r="E20" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="H20" s="74"/>
+      <c r="F20" s="74">
+        <v>2415000</v>
+      </c>
+      <c r="G20" s="68">
+        <f t="shared" si="4"/>
+        <v>1207500</v>
+      </c>
+      <c r="H20" s="68">
+        <v>1207000</v>
+      </c>
       <c r="I20" s="68">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M20" s="79"/>
-      <c r="N20" s="76"/>
-    </row>
-    <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+      <c r="J20" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="79"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="202"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="C21" s="78" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="D21" s="177"/>
-      <c r="E21" s="177"/>
-      <c r="F21" s="177"/>
-      <c r="G21" s="122" t="s">
+      <c r="E21" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="74"/>
+      <c r="F21" s="74">
+        <v>90000</v>
+      </c>
+      <c r="G21" s="68">
+        <f>IF(F21="",0,IF(F21&gt;=1700000,F21*O$19,F21*O$18))</f>
+        <v>54000</v>
+      </c>
+      <c r="H21" s="74">
+        <v>54000</v>
+      </c>
       <c r="I21" s="68">
-        <f>IF(H21="",0,IF(H21&gt;=1700000,H21*Q$19,H21*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="74"/>
-      <c r="K21" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M21" s="173"/>
-      <c r="N21" s="76"/>
-    </row>
-    <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="173"/>
+      <c r="L21" s="76"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="202"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
@@ -27778,22 +27727,20 @@
       <c r="D22" s="177"/>
       <c r="E22" s="177"/>
       <c r="F22" s="177"/>
-      <c r="G22" s="177"/>
+      <c r="G22" s="68">
+        <f>IF(F22="",0,IF(F22&gt;=1700000,F22*O$19,F22*O$18))</f>
+        <v>0</v>
+      </c>
       <c r="H22" s="177"/>
       <c r="I22" s="68">
-        <f>IF(H22="",0,IF(H22&gt;=1700000,H22*Q$19,H22*Q$18))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22" s="177"/>
-      <c r="K22" s="68">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="177"/>
-      <c r="M22" s="105"/>
-      <c r="N22" s="105"/>
-    </row>
-    <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="202"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
@@ -27803,85 +27750,89 @@
         <v>139</v>
       </c>
       <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66"/>
-      <c r="G23" s="75" t="s">
+      <c r="E23" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="133"/>
+      <c r="F23" s="133">
+        <v>1760000</v>
+      </c>
+      <c r="G23" s="68">
+        <f t="shared" ref="G23:G26" si="6">IF(F23="",0,IF(F23&gt;=1700000,F23*O$19,F23*O$18))</f>
+        <v>880000</v>
+      </c>
+      <c r="H23" s="132">
+        <v>880000</v>
+      </c>
       <c r="I23" s="68">
-        <f t="shared" ref="I23:I26" si="6">IF(H23="",0,IF(H23&gt;=1700000,H23*Q$19,H23*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="132"/>
-      <c r="K23" s="68">
-        <v>0</v>
-      </c>
-      <c r="L23" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M23" s="105"/>
-      <c r="N23" s="79"/>
-    </row>
-    <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="J23" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="105"/>
+      <c r="L23" s="79"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="202"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="65" t="s">
+        <v>148</v>
+      </c>
       <c r="D24" s="75"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="64" t="s">
+      <c r="E24" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="133"/>
+      <c r="F24" s="133">
+        <v>1840000</v>
+      </c>
+      <c r="G24" s="68">
+        <f t="shared" si="6"/>
+        <v>920000</v>
+      </c>
+      <c r="H24" s="133">
+        <v>920000</v>
+      </c>
       <c r="I24" s="68">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="133"/>
-      <c r="K24" s="68">
-        <f>I24-J24</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="69"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-    </row>
-    <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
+        <f>G24-H24</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="202"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="D25" s="73"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="178"/>
-      <c r="G25" s="75" t="s">
+      <c r="E25" s="75" t="s">
         <v>56</v>
+      </c>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68">
+        <f>IF(F25="",0,IF(F25&gt;=1700000,F25*O$19,F25*O$18))</f>
+        <v>0</v>
       </c>
       <c r="H25" s="68"/>
       <c r="I25" s="68">
-        <f>IF(H25="",0,IF(H25&gt;=1700000,H25*Q$19,H25*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L25" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-    </row>
-    <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="87"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="202"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
@@ -27890,59 +27841,64 @@
       <c r="C26" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="67">
-        <v>89078016404</v>
-      </c>
-      <c r="F26" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="66" t="s">
+      <c r="D26" s="66"/>
+      <c r="E26" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="H26" s="179"/>
+      <c r="F26" s="179">
+        <v>1730000</v>
+      </c>
+      <c r="G26" s="68">
+        <f t="shared" si="6"/>
+        <v>865000</v>
+      </c>
+      <c r="H26" s="133">
+        <v>865000</v>
+      </c>
       <c r="I26" s="68">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="133"/>
-      <c r="K26" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="M26" s="136"/>
-      <c r="N26" s="76"/>
-    </row>
-    <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="136"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="202"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="C27" s="177"/>
+      <c r="C27" s="78" t="s">
+        <v>131</v>
+      </c>
       <c r="D27" s="177"/>
-      <c r="E27" s="177"/>
-      <c r="F27" s="177"/>
-      <c r="G27" s="75" t="s">
+      <c r="E27" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="H27" s="177"/>
+      <c r="F27" s="74">
+        <v>1150000</v>
+      </c>
+      <c r="G27" s="68">
+        <f>IF(F27="",0,IF(F27&gt;=1700000,F27*O$19,F27*O$18))</f>
+        <v>690000</v>
+      </c>
+      <c r="H27" s="74">
+        <v>690000</v>
+      </c>
       <c r="I27" s="68">
-        <f>IF(H27="",0,IF(H27&gt;=1700000,H27*Q$19,H27*Q$18))</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="177"/>
-      <c r="K27" s="177"/>
-      <c r="L27" s="177"/>
-      <c r="M27" s="136"/>
-      <c r="N27" s="76"/>
-    </row>
-    <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="136"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="202"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
@@ -27956,12 +27912,10 @@
       <c r="H28" s="105"/>
       <c r="I28" s="105"/>
       <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="105"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="79"/>
-    </row>
-    <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K28" s="115"/>
+      <c r="L28" s="79"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="202"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
@@ -27975,12 +27929,10 @@
       <c r="H29" s="105"/>
       <c r="I29" s="105"/>
       <c r="J29" s="105"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="105"/>
-      <c r="M29" s="76"/>
-      <c r="N29" s="76"/>
-    </row>
-    <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K29" s="76"/>
+      <c r="L29" s="76"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="202"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
@@ -27989,18 +27941,16 @@
       <c r="C30" s="71"/>
       <c r="D30" s="73"/>
       <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="133"/>
       <c r="I30" s="132"/>
-      <c r="J30" s="133"/>
-      <c r="K30" s="132"/>
-      <c r="L30" s="131"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-    </row>
-    <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G39" s="25"/>
     </row>
@@ -28008,12 +27958,12 @@
   <mergeCells count="8">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="A7:A11"/>
-    <mergeCell ref="P10:Q11"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="P12:Q14"/>
-    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
     <mergeCell ref="A13:A30"/>
-    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="N15:O15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Theo dõi/T1 2026 02-01.xlsx
+++ b/Theo dõi/T1 2026 02-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA166D2-2BC8-4751-BC62-86E471F35EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346F0A09-DB96-4AC5-94D7-C080E03E283A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="16" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="biển số xe" sheetId="26" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <sheet name="27-01" sheetId="33" r:id="rId29"/>
     <sheet name="28-01" sheetId="34" r:id="rId30"/>
     <sheet name="29-01" sheetId="35" r:id="rId31"/>
+    <sheet name="30-01" sheetId="36" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="215">
   <si>
     <t>STT</t>
   </si>
@@ -682,6 +683,36 @@
   <si>
     <t>TRƯƠNG THANH TÚ</t>
   </si>
+  <si>
+    <t>68HC 001.70</t>
+  </si>
+  <si>
+    <t>68HC 001.93</t>
+  </si>
+  <si>
+    <t>68HC 001.89</t>
+  </si>
+  <si>
+    <t>LƯ HỚN VINH</t>
+  </si>
+  <si>
+    <t>DOANH THU 30/01/2026</t>
+  </si>
+  <si>
+    <t>nghỉ do con ốm</t>
+  </si>
+  <si>
+    <t>nghỉ do bệnh</t>
+  </si>
+  <si>
+    <t>thiếu 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thiếu 7k </t>
+  </si>
+  <si>
+    <t>VÕ ĐẸP</t>
+  </si>
 </sst>
 </file>
 
@@ -1218,7 +1249,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1716,6 +1747,45 @@
     <xf numFmtId="49" fontId="16" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="23" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4804,32 +4874,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -5496,20 +5566,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>16918000</v>
@@ -5646,32 +5716,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -6329,20 +6399,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -6491,18 +6561,18 @@
     </row>
     <row r="2" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -6511,18 +6581,18 @@
     </row>
     <row r="3" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -6616,7 +6686,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="204" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="98">
@@ -6661,7 +6731,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="190"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="70">
         <f>B7+1</f>
         <v>2</v>
@@ -6708,7 +6778,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="190"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B12" si="1">B8+1</f>
         <v>3</v>
@@ -6751,7 +6821,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="190"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="70">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6790,7 +6860,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="190"/>
+      <c r="A11" s="205"/>
       <c r="B11" s="64">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6833,7 +6903,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="70">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6876,7 +6946,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="190"/>
+      <c r="A13" s="205"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -6912,7 +6982,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64"/>
@@ -6932,7 +7002,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <v>1</v>
       </c>
@@ -6973,7 +7043,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f>B16+1</f>
         <v>2</v>
@@ -7015,7 +7085,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" ref="B18:B26" si="2">B17+1</f>
         <v>3</v>
@@ -7057,7 +7127,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7099,7 +7169,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7141,7 +7211,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7183,7 +7253,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7225,7 +7295,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7267,7 +7337,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7309,7 +7379,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="191"/>
+      <c r="A25" s="206"/>
       <c r="B25" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7351,7 +7421,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="191"/>
+      <c r="A26" s="206"/>
       <c r="B26" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7399,30 +7469,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="187" t="s">
+      <c r="H28" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="188"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29569000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="187" t="s">
+      <c r="H29" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="188"/>
+      <c r="I29" s="203"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17731000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="187" t="s">
+      <c r="H30" s="202" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="188"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17731000</v>
@@ -7503,18 +7573,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -7608,7 +7678,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="204" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -7654,7 +7724,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="190"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -7699,7 +7769,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="190"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -7738,7 +7808,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="190"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -7781,7 +7851,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="190"/>
+      <c r="A11" s="205"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -7824,7 +7894,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -7842,7 +7912,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="190"/>
+      <c r="A13" s="205"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -7878,7 +7948,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -7922,7 +7992,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -7965,7 +8035,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -8008,7 +8078,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -8051,7 +8121,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8094,7 +8164,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -8137,7 +8207,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -8181,7 +8251,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -8224,7 +8294,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -8267,7 +8337,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -8309,7 +8379,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="191"/>
+      <c r="A25" s="206"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -8352,7 +8422,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="191"/>
+      <c r="A26" s="206"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -8380,30 +8450,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="187" t="s">
+      <c r="H28" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="188"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29980000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="187" t="s">
+      <c r="H29" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="188"/>
+      <c r="I29" s="203"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17988000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="187" t="s">
+      <c r="H30" s="202" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="188"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>17996000</v>
@@ -8480,18 +8550,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -8585,7 +8655,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="204" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -8631,7 +8701,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="190"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -8676,7 +8746,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="190"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -8715,7 +8785,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="190"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -8758,7 +8828,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="190"/>
+      <c r="A11" s="205"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -8803,7 +8873,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -8821,7 +8891,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="190"/>
+      <c r="A13" s="205"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -8857,7 +8927,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -8901,7 +8971,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -8944,7 +9014,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -8987,7 +9057,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -9030,7 +9100,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -9073,7 +9143,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -9116,7 +9186,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -9159,7 +9229,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -9202,7 +9272,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -9245,7 +9315,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -9288,7 +9358,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="191"/>
+      <c r="A25" s="206"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -9331,7 +9401,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="191"/>
+      <c r="A26" s="206"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -9367,30 +9437,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="187" t="s">
+      <c r="H28" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="188"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31650000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="187" t="s">
+      <c r="H29" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="188"/>
+      <c r="I29" s="203"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18990000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="187" t="s">
+      <c r="H30" s="202" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="188"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>18990000</v>
@@ -9468,18 +9538,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -9573,7 +9643,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="204" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -9619,7 +9689,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="190"/>
+      <c r="A8" s="205"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -9664,7 +9734,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="190"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -9703,7 +9773,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="190"/>
+      <c r="A10" s="205"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -9746,7 +9816,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="190"/>
+      <c r="A11" s="205"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -9789,7 +9859,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -9807,7 +9877,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="190"/>
+      <c r="A13" s="205"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -9843,7 +9913,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="191" t="s">
+      <c r="A15" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -9886,7 +9956,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -9929,7 +9999,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -9972,7 +10042,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -10015,7 +10085,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -10058,7 +10128,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -10101,7 +10171,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -10146,7 +10216,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -10188,7 +10258,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -10231,7 +10301,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -10274,7 +10344,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="191"/>
+      <c r="A25" s="206"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -10317,7 +10387,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="191"/>
+      <c r="A26" s="206"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -10361,30 +10431,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="187" t="s">
+      <c r="H28" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="188"/>
+      <c r="I28" s="203"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29362000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="187" t="s">
+      <c r="H29" s="202" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="188"/>
+      <c r="I29" s="203"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17617200</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="187" t="s">
+      <c r="H30" s="202" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="188"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17619000</v>
@@ -10465,18 +10535,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -10570,7 +10640,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -10616,7 +10686,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -10663,7 +10733,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -10690,7 +10760,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -10730,17 +10800,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>28468000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -10780,9 +10850,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -10800,17 +10870,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>17080800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -10851,12 +10921,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -10896,12 +10966,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -10941,17 +11011,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>16486200</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -10994,7 +11064,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -11037,7 +11107,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -11080,7 +11150,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -11113,7 +11183,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -11156,7 +11226,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -11199,7 +11269,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -11241,7 +11311,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -11284,7 +11354,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -11340,7 +11410,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -11379,7 +11449,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -11418,7 +11488,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -11437,7 +11507,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -11456,7 +11526,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -11554,18 +11624,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -11659,7 +11729,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -11705,7 +11775,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -11748,7 +11818,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -11791,7 +11861,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11831,23 +11901,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>20755000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -11865,17 +11935,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>12453000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -11916,12 +11986,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -11961,12 +12031,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -12006,17 +12076,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>12451000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -12055,7 +12125,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -12098,7 +12168,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -12141,7 +12211,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -12184,7 +12254,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -12226,7 +12296,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -12269,7 +12339,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -12308,7 +12378,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -12329,7 +12399,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -12368,7 +12438,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -12405,7 +12475,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -12442,7 +12512,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -12475,7 +12545,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -12494,7 +12564,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -12593,18 +12663,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -12698,7 +12768,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -12744,7 +12814,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -12788,7 +12858,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -12831,7 +12901,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12871,23 +12941,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>29815000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -12905,17 +12975,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>17889000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -12956,12 +13026,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -12979,12 +13049,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -13024,17 +13094,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17728000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -13077,7 +13147,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -13120,7 +13190,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -13163,7 +13233,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -13206,7 +13276,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -13249,7 +13319,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -13292,7 +13362,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -13331,7 +13401,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -13352,7 +13422,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -13391,7 +13461,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -13428,7 +13498,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -13465,7 +13535,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -13500,7 +13570,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -13541,7 +13611,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -13642,18 +13712,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -13746,7 +13816,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -13792,7 +13862,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -13836,7 +13906,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -13879,7 +13949,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -13919,17 +13989,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>29241000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -13937,9 +14007,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -13957,17 +14027,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>17544600</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -14008,12 +14078,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -14031,12 +14101,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -14076,17 +14146,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17384600</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -14129,7 +14199,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -14172,7 +14242,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -14215,7 +14285,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -14258,7 +14328,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -14301,7 +14371,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -14344,7 +14414,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -14383,7 +14453,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -14404,7 +14474,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -14443,7 +14513,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -14481,7 +14551,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -14518,7 +14588,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -14552,7 +14622,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -14593,7 +14663,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -14665,32 +14735,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -15261,20 +15331,20 @@
       <c r="F25" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="186" t="s">
+      <c r="H25" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="186"/>
+      <c r="I25" s="201"/>
       <c r="J25" s="9">
         <f>SUM(H7:H1000)</f>
         <v>24820000</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(I7:I1000)</f>
         <v>14390000</v>
@@ -15417,18 +15487,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -15521,7 +15591,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -15569,7 +15639,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -15615,7 +15685,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -15658,7 +15728,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -15698,17 +15768,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>39465000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -15716,9 +15786,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -15736,17 +15806,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>23679000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -15787,12 +15857,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -15813,12 +15883,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -15858,17 +15928,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>23501000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -15911,7 +15981,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -15954,7 +16024,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -15997,7 +16067,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -16040,7 +16110,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -16083,7 +16153,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -16126,7 +16196,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16165,7 +16235,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -16186,7 +16256,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -16225,7 +16295,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -16263,7 +16333,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -16300,7 +16370,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -16335,7 +16405,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -16377,7 +16447,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -16477,18 +16547,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -16581,7 +16651,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -16627,7 +16697,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -16673,7 +16743,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -16716,7 +16786,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16756,17 +16826,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>28993000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -16774,9 +16844,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -16794,17 +16864,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>17395800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -16845,12 +16915,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="191"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -16871,12 +16941,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="191"/>
+      <c r="A15" s="206"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -16916,17 +16986,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17285000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="191"/>
+      <c r="A16" s="206"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -16969,7 +17039,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="191"/>
+      <c r="A17" s="206"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -17014,7 +17084,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="191"/>
+      <c r="A18" s="206"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -17057,7 +17127,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="191"/>
+      <c r="A19" s="206"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -17100,7 +17170,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="191"/>
+      <c r="A20" s="206"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -17143,7 +17213,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="191"/>
+      <c r="A21" s="206"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -17186,7 +17256,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="191"/>
+      <c r="A22" s="206"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17225,7 +17295,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="191"/>
+      <c r="A23" s="206"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -17246,7 +17316,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="191"/>
+      <c r="A24" s="206"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -17285,7 +17355,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="207" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -17323,7 +17393,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="193"/>
+      <c r="A27" s="208"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -17360,7 +17430,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="193"/>
+      <c r="A28" s="208"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -17395,7 +17465,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="193"/>
+      <c r="A29" s="208"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -17436,7 +17506,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="193"/>
+      <c r="A30" s="208"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -17536,18 +17606,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -17640,7 +17710,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -17686,7 +17756,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -17732,7 +17802,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -17775,7 +17845,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -17815,17 +17885,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>23968000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -17833,9 +17903,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -17853,17 +17923,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>14380800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -17906,12 +17976,12 @@
       </c>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -17952,12 +18022,12 @@
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -17997,17 +18067,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14555400</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -18050,7 +18120,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -18089,7 +18159,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -18132,7 +18202,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -18175,7 +18245,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -18218,7 +18288,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -18257,7 +18327,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -18278,7 +18348,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -18299,7 +18369,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -18320,7 +18390,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -18341,7 +18411,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -18379,7 +18449,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -18416,7 +18486,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -18451,7 +18521,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -18492,7 +18562,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -18526,14 +18596,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="P12:Q14"/>
-    <mergeCell ref="R12:R14"/>
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="A13:A30"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="P10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="P12:Q14"/>
+    <mergeCell ref="R12:R14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18591,18 +18661,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -18695,7 +18765,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -18737,7 +18807,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -18783,7 +18853,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -18826,7 +18896,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -18866,17 +18936,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>25750000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -18884,9 +18954,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -18904,17 +18974,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>15450000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -18955,12 +19025,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -19000,12 +19070,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -19045,17 +19115,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>15330000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -19076,7 +19146,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -19119,7 +19189,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -19162,7 +19232,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -19205,7 +19275,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -19248,7 +19318,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -19287,7 +19357,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -19308,7 +19378,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -19345,7 +19415,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -19382,7 +19452,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -19419,7 +19489,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -19461,7 +19531,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -19484,7 +19554,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -19503,7 +19573,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -19522,7 +19592,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -19621,18 +19691,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -19725,7 +19795,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -19771,7 +19841,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -19817,7 +19887,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -19860,7 +19930,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -19900,17 +19970,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="200" t="s">
+      <c r="P10" s="215" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="200"/>
-      <c r="R10" s="195">
+      <c r="Q10" s="215"/>
+      <c r="R10" s="210">
         <f>SUM(H7:H999)</f>
         <v>24922000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -19918,9 +19988,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="200"/>
-      <c r="R11" s="195"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="215"/>
+      <c r="R11" s="210"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -19938,17 +20008,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="194" t="s">
+      <c r="P12" s="209" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="194"/>
-      <c r="R12" s="195">
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210">
         <f>SUM(I7:I999)</f>
         <v>14953200</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -19989,12 +20059,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="194"/>
-      <c r="Q13" s="194"/>
-      <c r="R13" s="195"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -20034,12 +20104,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="194"/>
-      <c r="Q14" s="194"/>
-      <c r="R14" s="195"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -20079,17 +20149,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="196" t="s">
+      <c r="P15" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="196"/>
+      <c r="Q15" s="211"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14843000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -20110,7 +20180,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -20153,7 +20223,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -20198,7 +20268,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -20243,7 +20313,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -20286,7 +20356,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -20325,7 +20395,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -20346,7 +20416,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -20385,7 +20455,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -20424,7 +20494,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -20461,7 +20531,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -20504,7 +20574,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -20527,7 +20597,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -20546,7 +20616,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -20565,7 +20635,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -20640,18 +20710,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -20711,7 +20781,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -20756,7 +20826,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -20802,7 +20872,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="1">B8+1</f>
         <v>3</v>
@@ -20843,7 +20913,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -20882,26 +20952,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>21305000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -20918,17 +20988,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>12783000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -20968,12 +21038,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -21012,12 +21082,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="3">B14+1</f>
         <v>3</v>
@@ -21056,17 +21126,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12675000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -21088,7 +21158,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -21129,7 +21199,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -21176,7 +21246,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -21225,7 +21295,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -21266,7 +21336,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -21303,7 +21373,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -21325,7 +21395,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -21352,7 +21422,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -21379,7 +21449,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -21414,7 +21484,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -21455,7 +21525,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -21476,7 +21546,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -21495,7 +21565,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -21514,7 +21584,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -21579,18 +21649,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -21650,7 +21720,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -21695,7 +21765,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -21739,7 +21809,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -21780,7 +21850,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -21819,26 +21889,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>25660000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -21855,17 +21925,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>13375000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -21905,12 +21975,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -21949,12 +22019,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -21993,17 +22063,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13500000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -22028,7 +22098,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -22069,7 +22139,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -22121,7 +22191,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -22173,7 +22243,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -22214,7 +22284,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -22251,7 +22321,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -22276,7 +22346,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -22303,7 +22373,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -22330,7 +22400,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -22365,7 +22435,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -22406,7 +22476,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -22430,7 +22500,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -22449,7 +22519,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -22468,7 +22538,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -22533,18 +22603,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -22604,7 +22674,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -22651,7 +22721,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -22695,7 +22765,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -22736,7 +22806,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -22775,26 +22845,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>25245000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -22811,17 +22881,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>13121500</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -22861,12 +22931,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -22905,12 +22975,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -22949,17 +23019,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13128000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -22984,7 +23054,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -23025,7 +23095,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -23071,7 +23141,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -23121,7 +23191,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -23162,7 +23232,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -23199,7 +23269,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -23224,7 +23294,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -23251,7 +23321,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -23278,7 +23348,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -23313,7 +23383,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -23354,7 +23424,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -23378,7 +23448,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -23397,7 +23467,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -23416,7 +23486,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -23481,18 +23551,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -23552,7 +23622,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -23599,7 +23669,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -23645,7 +23715,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -23688,7 +23758,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -23727,26 +23797,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>22790000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -23763,17 +23833,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>12103000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -23813,12 +23883,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -23857,12 +23927,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -23901,17 +23971,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12000000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -23936,7 +24006,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -23977,7 +24047,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -24023,7 +24093,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -24073,7 +24143,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -24114,7 +24184,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -24151,7 +24221,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -24176,7 +24246,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -24203,7 +24273,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -24230,7 +24300,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -24265,7 +24335,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -24306,7 +24376,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -24330,7 +24400,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -24349,7 +24419,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -24368,7 +24438,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -24433,18 +24503,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -24504,7 +24574,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -24549,7 +24619,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -24585,7 +24655,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -24627,7 +24697,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -24668,17 +24738,17 @@
         <v>192</v>
       </c>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>18585000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -24691,9 +24761,9 @@
       <c r="L11" s="175"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -24710,17 +24780,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>10091000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -24760,12 +24830,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -24804,12 +24874,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -24850,17 +24920,17 @@
         <v>191</v>
       </c>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>10021000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -24885,7 +24955,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -24926,7 +24996,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -24968,7 +25038,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -25020,7 +25090,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -25061,7 +25131,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -25096,7 +25166,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -25121,7 +25191,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -25148,7 +25218,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -25175,7 +25245,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -25210,7 +25280,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -25251,7 +25321,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -25275,7 +25345,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -25294,7 +25364,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -25313,7 +25383,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -25337,6 +25407,7 @@
       <c r="G39" s="25"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="A7:A11"/>
@@ -25375,32 +25446,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -26069,20 +26140,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29135000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17346000</v>
@@ -26207,18 +26278,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -26278,7 +26349,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -26323,7 +26394,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -26359,7 +26430,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -26401,7 +26472,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -26440,17 +26511,17 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="203" t="s">
+      <c r="P10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="203"/>
-      <c r="R10" s="204">
+      <c r="Q10" s="218"/>
+      <c r="R10" s="219">
         <f>SUM(H7:H999)</f>
         <v>18425000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -26463,9 +26534,9 @@
       <c r="L11" s="175"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="204"/>
+      <c r="P11" s="218"/>
+      <c r="Q11" s="218"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -26482,17 +26553,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="205" t="s">
+      <c r="P12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="205"/>
-      <c r="R12" s="204">
+      <c r="Q12" s="220"/>
+      <c r="R12" s="219">
         <f>SUM(I7:I999)</f>
         <v>10290500</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -26532,12 +26603,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="205"/>
-      <c r="Q13" s="205"/>
-      <c r="R13" s="204"/>
+      <c r="P13" s="220"/>
+      <c r="Q13" s="220"/>
+      <c r="R13" s="219"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -26576,12 +26647,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="205"/>
-      <c r="Q14" s="205"/>
-      <c r="R14" s="204"/>
+      <c r="P14" s="220"/>
+      <c r="Q14" s="220"/>
+      <c r="R14" s="219"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -26620,17 +26691,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="206" t="s">
+      <c r="P15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="206"/>
+      <c r="Q15" s="221"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>10183000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -26655,7 +26726,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -26696,7 +26767,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -26738,7 +26809,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -26790,7 +26861,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -26831,7 +26902,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -26862,7 +26933,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -26887,7 +26958,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -26923,7 +26994,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -26950,7 +27021,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -26985,7 +27056,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -27026,7 +27097,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -27050,7 +27121,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -27069,7 +27140,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -27088,7 +27159,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -27112,6 +27183,7 @@
       <c r="G39" s="25"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="8">
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="A7:A11"/>
@@ -27153,24 +27225,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="183"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="183"/>
-      <c r="F3" s="183"/>
-      <c r="G3" s="183"/>
-      <c r="H3" s="183"/>
-      <c r="I3" s="183"/>
-      <c r="J3" s="183"/>
-      <c r="K3" s="183"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
       <c r="D4" s="117"/>
       <c r="E4" s="117"/>
-      <c r="H4" s="116" t="s">
+      <c r="F4" s="116" t="s">
         <v>199</v>
       </c>
       <c r="I4" s="117"/>
@@ -27218,7 +27290,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
+      <c r="A7" s="212" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -27255,7 +27327,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="198"/>
+      <c r="A8" s="213"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -27293,7 +27365,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="198"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -27325,7 +27397,7 @@
       <c r="L9" s="79"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="198"/>
+      <c r="A10" s="213"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -27356,17 +27428,17 @@
       </c>
       <c r="K10" s="76"/>
       <c r="L10" s="76"/>
-      <c r="N10" s="203" t="s">
+      <c r="N10" s="218" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="203"/>
-      <c r="P10" s="204">
+      <c r="O10" s="218"/>
+      <c r="P10" s="219">
         <f>SUM(H7:H999)</f>
         <v>12810000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="199"/>
+      <c r="A11" s="214"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -27377,9 +27449,9 @@
       <c r="J11" s="175"/>
       <c r="K11" s="79"/>
       <c r="L11" s="79"/>
-      <c r="N11" s="203"/>
-      <c r="O11" s="203"/>
-      <c r="P11" s="204"/>
+      <c r="N11" s="218"/>
+      <c r="O11" s="218"/>
+      <c r="P11" s="219"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -27394,17 +27466,17 @@
       <c r="J12" s="96"/>
       <c r="K12" s="97"/>
       <c r="L12" s="97"/>
-      <c r="N12" s="205" t="s">
+      <c r="N12" s="220" t="s">
         <v>143</v>
       </c>
-      <c r="O12" s="205"/>
-      <c r="P12" s="204">
+      <c r="O12" s="220"/>
+      <c r="P12" s="219">
         <f>SUM(I7:I999)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="201" t="s">
+      <c r="A13" s="216" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -27438,12 +27510,12 @@
         <v>202</v>
       </c>
       <c r="L13" s="76"/>
-      <c r="N13" s="205"/>
-      <c r="O13" s="205"/>
-      <c r="P13" s="204"/>
+      <c r="N13" s="220"/>
+      <c r="O13" s="220"/>
+      <c r="P13" s="219"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="202"/>
+      <c r="A14" s="217"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -27474,12 +27546,12 @@
       </c>
       <c r="K14" s="79"/>
       <c r="L14" s="79"/>
-      <c r="N14" s="205"/>
-      <c r="O14" s="205"/>
-      <c r="P14" s="204"/>
+      <c r="N14" s="220"/>
+      <c r="O14" s="220"/>
+      <c r="P14" s="219"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="202"/>
+      <c r="A15" s="217"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -27510,17 +27582,17 @@
       </c>
       <c r="K15" s="76"/>
       <c r="L15" s="85"/>
-      <c r="N15" s="206" t="s">
+      <c r="N15" s="221" t="s">
         <v>117</v>
       </c>
-      <c r="O15" s="206"/>
+      <c r="O15" s="221"/>
       <c r="P15" s="160">
         <f>SUM(J7:J98)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202"/>
+      <c r="A16" s="217"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -27543,7 +27615,7 @@
       <c r="L16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202"/>
+      <c r="A17" s="217"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -27576,7 +27648,7 @@
       <c r="L17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="202"/>
+      <c r="A18" s="217"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -27610,7 +27682,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="202"/>
+      <c r="A19" s="217"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -27652,7 +27724,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="202"/>
+      <c r="A20" s="217"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -27685,7 +27757,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="202"/>
+      <c r="A21" s="217"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -27718,7 +27790,7 @@
       <c r="L21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="202"/>
+      <c r="A22" s="217"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -27741,7 +27813,7 @@
       <c r="L22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="202"/>
+      <c r="A23" s="217"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -27773,7 +27845,7 @@
       <c r="L23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="202"/>
+      <c r="A24" s="217"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -27806,7 +27878,7 @@
       <c r="L24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="202"/>
+      <c r="A25" s="217"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -27833,7 +27905,7 @@
       <c r="L25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="202"/>
+      <c r="A26" s="217"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -27866,7 +27938,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="202"/>
+      <c r="A27" s="217"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -27899,7 +27971,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="202"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -27916,7 +27988,7 @@
       <c r="L28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="202"/>
+      <c r="A29" s="217"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -27933,7 +28005,845 @@
       <c r="L29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="202"/>
+      <c r="A30" s="217"/>
+      <c r="B30" s="64">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="133"/>
+      <c r="I30" s="132"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="8">
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="A13:A30"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56DAE672-D35B-4A22-945E-F7CA37050AA8}">
+  <dimension ref="A3:Q39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="35.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="19.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="198" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="198"/>
+      <c r="I3" s="198"/>
+      <c r="J3" s="198"/>
+      <c r="K3" s="198"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="116" t="s">
+        <v>209</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="158" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="158" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="158" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="158" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="212" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="66"/>
+      <c r="E7" s="192" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="68">
+        <v>1300000</v>
+      </c>
+      <c r="G7" s="68">
+        <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
+        <v>780000</v>
+      </c>
+      <c r="H7" s="68">
+        <v>780000</v>
+      </c>
+      <c r="I7" s="68">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="136"/>
+      <c r="L7" s="76"/>
+      <c r="N7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="213"/>
+      <c r="B8" s="64">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="65"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="193" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68">
+        <f t="shared" ref="G8:G10" si="0">IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68">
+        <f t="shared" ref="I8:I10" si="1">G8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="69"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="N8" s="82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="213"/>
+      <c r="B9" s="64">
+        <f t="shared" ref="B9:B10" si="2">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="66"/>
+      <c r="E9" s="192" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="68">
+        <v>1150000</v>
+      </c>
+      <c r="G9" s="68">
+        <f t="shared" si="0"/>
+        <v>690000</v>
+      </c>
+      <c r="H9" s="74">
+        <v>690000</v>
+      </c>
+      <c r="I9" s="68">
+        <v>0</v>
+      </c>
+      <c r="J9" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="76"/>
+      <c r="L9" s="79"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="213"/>
+      <c r="B10" s="64">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="73"/>
+      <c r="E10" s="194" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="74">
+        <v>1000000</v>
+      </c>
+      <c r="G10" s="68">
+        <f t="shared" si="0"/>
+        <v>600000</v>
+      </c>
+      <c r="H10" s="74">
+        <v>600000</v>
+      </c>
+      <c r="I10" s="68">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="N10" s="218" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="218"/>
+      <c r="P10" s="219">
+        <f>SUM(F7:F999)</f>
+        <v>25582000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="214"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="195"/>
+      <c r="F11" s="176"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="N11" s="218"/>
+      <c r="O11" s="218"/>
+      <c r="P11" s="219"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="107"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="147"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="N12" s="220" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" s="220"/>
+      <c r="P12" s="219">
+        <f>SUM(G7:G999)</f>
+        <v>13354000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="216" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="66"/>
+      <c r="E13" s="192" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="68">
+        <v>1720000</v>
+      </c>
+      <c r="G13" s="68">
+        <f>IF(F13="",0,IF(F13&gt;=1700000,F13*O$19,F13*O$18))</f>
+        <v>860000</v>
+      </c>
+      <c r="H13" s="68">
+        <v>860000</v>
+      </c>
+      <c r="I13" s="68">
+        <f t="shared" ref="I13:I27" si="3">G13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="76"/>
+      <c r="L13" s="76"/>
+      <c r="N13" s="220"/>
+      <c r="O13" s="220"/>
+      <c r="P13" s="219"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="217"/>
+      <c r="B14" s="64">
+        <f>B13+1</f>
+        <v>2</v>
+      </c>
+      <c r="C14" s="78" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="194" t="s">
+        <v>206</v>
+      </c>
+      <c r="F14" s="74">
+        <v>2380000</v>
+      </c>
+      <c r="G14" s="68">
+        <f t="shared" ref="G14:G20" si="4">IF(F14="",0,IF(F14&gt;=1700000,F14*O$19,F14*O$18))</f>
+        <v>1190000</v>
+      </c>
+      <c r="H14" s="74">
+        <v>1190000</v>
+      </c>
+      <c r="I14" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="N14" s="220"/>
+      <c r="O14" s="220"/>
+      <c r="P14" s="219"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="217"/>
+      <c r="B15" s="64">
+        <f t="shared" ref="B15:B30" si="5">B14+1</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="183" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="184"/>
+      <c r="E15" s="196" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="112"/>
+      <c r="I15" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="190"/>
+      <c r="K15" s="188" t="s">
+        <v>210</v>
+      </c>
+      <c r="L15" s="85"/>
+      <c r="N15" s="221" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="221"/>
+      <c r="P15" s="160">
+        <f>SUM(H7:H999)</f>
+        <v>13332000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="217"/>
+      <c r="B16" s="64">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="C16" s="77"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68">
+        <f>IF(F16="",0,IF(F16&gt;=1700000,F16*O$19,F16*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="69"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="217"/>
+      <c r="B17" s="64">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="75"/>
+      <c r="E17" s="193" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="68">
+        <v>3497000</v>
+      </c>
+      <c r="G17" s="68">
+        <f t="shared" si="4"/>
+        <v>1748500</v>
+      </c>
+      <c r="H17" s="74">
+        <v>1749000</v>
+      </c>
+      <c r="I17" s="68">
+        <f t="shared" si="3"/>
+        <v>-500</v>
+      </c>
+      <c r="J17" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="80"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="217"/>
+      <c r="B18" s="64">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" s="75"/>
+      <c r="E18" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="68">
+        <v>380000</v>
+      </c>
+      <c r="G18" s="68">
+        <f>IF(F18="",0,IF(F18&gt;=1700000,F18*O$19,F18*O$18))</f>
+        <v>228000</v>
+      </c>
+      <c r="H18" s="74">
+        <v>228000</v>
+      </c>
+      <c r="I18" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="131"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="76"/>
+      <c r="N18" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="162">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="164" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="217"/>
+      <c r="B19" s="64">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="64"/>
+      <c r="E19" s="80" t="s">
+        <v>205</v>
+      </c>
+      <c r="F19" s="68">
+        <v>1750000</v>
+      </c>
+      <c r="G19" s="68">
+        <f t="shared" si="4"/>
+        <v>875000</v>
+      </c>
+      <c r="H19" s="68">
+        <v>860000</v>
+      </c>
+      <c r="I19" s="68">
+        <f t="shared" si="3"/>
+        <v>15000</v>
+      </c>
+      <c r="J19" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="L19" s="76"/>
+      <c r="N19" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="164" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="217"/>
+      <c r="B20" s="64">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="80" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="74">
+        <v>3000000</v>
+      </c>
+      <c r="G20" s="68">
+        <f t="shared" si="4"/>
+        <v>1500000</v>
+      </c>
+      <c r="H20" s="68">
+        <v>1500000</v>
+      </c>
+      <c r="I20" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="79"/>
+      <c r="L20" s="76"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="217"/>
+      <c r="B21" s="64">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="C21" s="185" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="186"/>
+      <c r="E21" s="187" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="112"/>
+      <c r="G21" s="119">
+        <f>IF(F21="",0,IF(F21&gt;=1700000,F21*O$19,F21*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="112"/>
+      <c r="I21" s="119">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="190"/>
+      <c r="K21" s="189" t="s">
+        <v>211</v>
+      </c>
+      <c r="L21" s="76"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="217"/>
+      <c r="B22" s="64">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="177"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="197"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="68">
+        <f>IF(F22="",0,IF(F22&gt;=1700000,F22*O$19,F22*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="177"/>
+      <c r="I22" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="177"/>
+      <c r="K22" s="191"/>
+      <c r="L22" s="105"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="217"/>
+      <c r="B23" s="64">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="66"/>
+      <c r="E23" s="193" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="133">
+        <v>1730000</v>
+      </c>
+      <c r="G23" s="68">
+        <f t="shared" ref="G23:G26" si="6">IF(F23="",0,IF(F23&gt;=1700000,F23*O$19,F23*O$18))</f>
+        <v>865000</v>
+      </c>
+      <c r="H23" s="132">
+        <v>865000</v>
+      </c>
+      <c r="I23" s="68">
+        <v>0</v>
+      </c>
+      <c r="J23" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="191"/>
+      <c r="L23" s="79"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="217"/>
+      <c r="B24" s="64">
+        <f t="shared" si="5"/>
+        <v>12</v>
+      </c>
+      <c r="C24" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="75"/>
+      <c r="E24" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" s="133">
+        <v>3815000</v>
+      </c>
+      <c r="G24" s="68">
+        <f t="shared" si="6"/>
+        <v>1907500</v>
+      </c>
+      <c r="H24" s="133">
+        <v>1900000</v>
+      </c>
+      <c r="I24" s="68">
+        <f>G24-H24</f>
+        <v>7500</v>
+      </c>
+      <c r="J24" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" s="191" t="s">
+        <v>213</v>
+      </c>
+      <c r="L24" s="105"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="217"/>
+      <c r="B25" s="64">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="D25" s="73"/>
+      <c r="E25" s="193" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" s="68">
+        <v>660000</v>
+      </c>
+      <c r="G25" s="68">
+        <f>IF(F25="",0,IF(F25&gt;=1700000,F25*O$19,F25*O$18))</f>
+        <v>396000</v>
+      </c>
+      <c r="H25" s="68">
+        <v>396000</v>
+      </c>
+      <c r="I25" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="87"/>
+      <c r="K25" s="191"/>
+      <c r="L25" s="105"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="217"/>
+      <c r="B26" s="64">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="C26" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="66"/>
+      <c r="E26" s="192" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="179">
+        <v>1140000</v>
+      </c>
+      <c r="G26" s="68">
+        <f t="shared" si="6"/>
+        <v>684000</v>
+      </c>
+      <c r="H26" s="133">
+        <v>684000</v>
+      </c>
+      <c r="I26" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="136"/>
+      <c r="L26" s="76"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="217"/>
+      <c r="B27" s="64">
+        <f t="shared" si="5"/>
+        <v>15</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="177"/>
+      <c r="E27" s="193" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="74">
+        <v>2060000</v>
+      </c>
+      <c r="G27" s="68">
+        <f>IF(F27="",0,IF(F27&gt;=1700000,F27*O$19,F27*O$18))</f>
+        <v>1030000</v>
+      </c>
+      <c r="H27" s="74">
+        <v>1030000</v>
+      </c>
+      <c r="I27" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="136"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="217"/>
+      <c r="B28" s="64">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="115"/>
+      <c r="L28" s="79"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="217"/>
+      <c r="B29" s="64">
+        <f t="shared" si="5"/>
+        <v>17</v>
+      </c>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="105"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="76"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="217"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -27993,32 +28903,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -28683,20 +29593,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32170000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19075000</v>
@@ -28817,32 +29727,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -29494,20 +30404,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30806000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18342000</v>
@@ -29628,32 +30538,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -30300,20 +31210,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30762000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18280000</v>
@@ -30437,32 +31347,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -31115,20 +32025,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31566000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18200000</v>
@@ -31252,32 +32162,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -31927,20 +32837,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18612000</v>
@@ -32066,32 +32976,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="183" t="s">
+      <c r="B2" s="198" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="199" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
+      <c r="C3" s="200"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="200"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="200"/>
+      <c r="J3" s="200"/>
+      <c r="K3" s="200"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -32753,20 +33663,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="186" t="s">
+      <c r="H26" s="201" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="186"/>
+      <c r="I26" s="201"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32130000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="186" t="s">
+      <c r="H27" s="201" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="186"/>
+      <c r="I27" s="201"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19110000</v>

--- a/Theo dõi/T1 2026 02-01.xlsx
+++ b/Theo dõi/T1 2026 02-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346F0A09-DB96-4AC5-94D7-C080E03E283A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384963EE-C5D9-4ED6-9C93-10A7451DFD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="18" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="biển số xe" sheetId="26" r:id="rId1"/>
@@ -45,6 +45,7 @@
     <sheet name="28-01" sheetId="34" r:id="rId30"/>
     <sheet name="29-01" sheetId="35" r:id="rId31"/>
     <sheet name="30-01" sheetId="36" r:id="rId32"/>
+    <sheet name="31-01" sheetId="37" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3490" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="222">
   <si>
     <t>STT</t>
   </si>
@@ -713,6 +714,27 @@
   <si>
     <t>VÕ ĐẸP</t>
   </si>
+  <si>
+    <t>DOANH THU 31/01/2026</t>
+  </si>
+  <si>
+    <t>ĐỖ VIẾT BÌNH</t>
+  </si>
+  <si>
+    <t>NGỌC TỈNH</t>
+  </si>
+  <si>
+    <t>qua tháng nghỉ</t>
+  </si>
+  <si>
+    <t>NGUYỄN TẤN THÀNH</t>
+  </si>
+  <si>
+    <t>NGUYỄN THANH LIÊM</t>
+  </si>
+  <si>
+    <t>ngày mai mới làm</t>
+  </si>
 </sst>
 </file>
 
@@ -721,7 +743,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,000"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -957,8 +979,47 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1083,8 +1144,20 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1242,6 +1315,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1249,7 +1342,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="267">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1786,6 +1879,129 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="35" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="35" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="35" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="35" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="37" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="35" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="35" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1857,6 +2073,12 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="3" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4874,32 +5096,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -5566,20 +5788,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>16918000</v>
@@ -5716,32 +5938,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -6399,20 +6621,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>28869000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17311000</v>
@@ -6561,18 +6783,18 @@
     </row>
     <row r="2" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -6581,18 +6803,18 @@
     </row>
     <row r="3" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -6686,7 +6908,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="247" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="98">
@@ -6731,7 +6953,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="205"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="70">
         <f>B7+1</f>
         <v>2</v>
@@ -6778,7 +7000,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="205"/>
+      <c r="A9" s="248"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B12" si="1">B8+1</f>
         <v>3</v>
@@ -6821,7 +7043,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="205"/>
+      <c r="A10" s="248"/>
       <c r="B10" s="70">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6860,7 +7082,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="205"/>
+      <c r="A11" s="248"/>
       <c r="B11" s="64">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -6903,7 +7125,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="70">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6946,7 +7168,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
+      <c r="A13" s="248"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -6982,7 +7204,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="206" t="s">
+      <c r="A15" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64"/>
@@ -7002,7 +7224,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <v>1</v>
       </c>
@@ -7043,7 +7265,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f>B16+1</f>
         <v>2</v>
@@ -7085,7 +7307,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" ref="B18:B26" si="2">B17+1</f>
         <v>3</v>
@@ -7127,7 +7349,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -7169,7 +7391,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -7211,7 +7433,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -7253,7 +7475,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -7295,7 +7517,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -7337,7 +7559,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -7379,7 +7601,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="206"/>
+      <c r="A25" s="249"/>
       <c r="B25" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -7421,7 +7643,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
+      <c r="A26" s="249"/>
       <c r="B26" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -7469,30 +7691,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="202" t="s">
+      <c r="H28" s="245" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="203"/>
+      <c r="I28" s="246"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29569000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="202" t="s">
+      <c r="H29" s="245" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="203"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17731000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="202" t="s">
+      <c r="H30" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="203"/>
+      <c r="I30" s="246"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17731000</v>
@@ -7573,18 +7795,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -7678,7 +7900,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="247" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -7724,7 +7946,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="205"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -7769,7 +7991,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="205"/>
+      <c r="A9" s="248"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -7808,7 +8030,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="205"/>
+      <c r="A10" s="248"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -7851,7 +8073,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="205"/>
+      <c r="A11" s="248"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -7894,7 +8116,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -7912,7 +8134,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
+      <c r="A13" s="248"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -7948,7 +8170,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="206" t="s">
+      <c r="A15" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -7992,7 +8214,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -8035,7 +8257,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -8078,7 +8300,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -8121,7 +8343,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -8164,7 +8386,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -8207,7 +8429,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -8251,7 +8473,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -8294,7 +8516,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -8337,7 +8559,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -8379,7 +8601,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="206"/>
+      <c r="A25" s="249"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -8422,7 +8644,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
+      <c r="A26" s="249"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -8450,30 +8672,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="202" t="s">
+      <c r="H28" s="245" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="203"/>
+      <c r="I28" s="246"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29980000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="202" t="s">
+      <c r="H29" s="245" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="203"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17988000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="202" t="s">
+      <c r="H30" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="203"/>
+      <c r="I30" s="246"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>17996000</v>
@@ -8550,18 +8772,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -8655,7 +8877,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="247" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -8701,7 +8923,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="205"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -8746,7 +8968,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="205"/>
+      <c r="A9" s="248"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -8785,7 +9007,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="205"/>
+      <c r="A10" s="248"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -8828,7 +9050,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="205"/>
+      <c r="A11" s="248"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -8873,7 +9095,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -8891,7 +9113,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
+      <c r="A13" s="248"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -8927,7 +9149,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="206" t="s">
+      <c r="A15" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -8971,7 +9193,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -9014,7 +9236,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -9057,7 +9279,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -9100,7 +9322,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -9143,7 +9365,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -9186,7 +9408,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -9229,7 +9451,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -9272,7 +9494,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -9315,7 +9537,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -9358,7 +9580,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="206"/>
+      <c r="A25" s="249"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -9401,7 +9623,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
+      <c r="A26" s="249"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -9437,30 +9659,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="202" t="s">
+      <c r="H28" s="245" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="203"/>
+      <c r="I28" s="246"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31650000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="202" t="s">
+      <c r="H29" s="245" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="203"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18990000</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="202" t="s">
+      <c r="H30" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="203"/>
+      <c r="I30" s="246"/>
       <c r="J30" s="63">
         <f>SUM(J7:J25)</f>
         <v>18990000</v>
@@ -9538,18 +9760,18 @@
     </row>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -9643,7 +9865,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="204" t="s">
+      <c r="A7" s="247" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -9689,7 +9911,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="205"/>
+      <c r="A8" s="248"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -9734,7 +9956,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="205"/>
+      <c r="A9" s="248"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -9773,7 +9995,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="205"/>
+      <c r="A10" s="248"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -9816,7 +10038,7 @@
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="205"/>
+      <c r="A11" s="248"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -9859,7 +10081,7 @@
       <c r="P11" s="1"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="248"/>
       <c r="B12" s="105"/>
       <c r="C12" s="105"/>
       <c r="D12" s="105"/>
@@ -9877,7 +10099,7 @@
       <c r="P12" s="1"/>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="205"/>
+      <c r="A13" s="248"/>
       <c r="B13" s="64"/>
       <c r="C13" s="65"/>
       <c r="D13" s="66"/>
@@ -9913,7 +10135,7 @@
       <c r="P14" s="1"/>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="206" t="s">
+      <c r="A15" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B15" s="64">
@@ -9956,7 +10178,7 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f>B15+1</f>
         <v>2</v>
@@ -9999,7 +10221,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" ref="B17:B26" si="3">B16+1</f>
         <v>3</v>
@@ -10042,7 +10264,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -10085,7 +10307,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -10128,7 +10350,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -10171,7 +10393,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -10216,7 +10438,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -10258,7 +10480,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -10301,7 +10523,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -10344,7 +10566,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="206"/>
+      <c r="A25" s="249"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -10387,7 +10609,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="206"/>
+      <c r="A26" s="249"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -10431,30 +10653,30 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H28" s="202" t="s">
+      <c r="H28" s="245" t="s">
         <v>29</v>
       </c>
-      <c r="I28" s="203"/>
+      <c r="I28" s="246"/>
       <c r="J28" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29362000</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H29" s="202" t="s">
+      <c r="H29" s="245" t="s">
         <v>30</v>
       </c>
-      <c r="I29" s="203"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17617200</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H30" s="202" t="s">
+      <c r="H30" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="I30" s="203"/>
+      <c r="I30" s="246"/>
       <c r="J30" s="63">
         <f>SUM(J7:J26)</f>
         <v>17619000</v>
@@ -10535,18 +10757,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -10640,7 +10862,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -10686,7 +10908,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -10733,7 +10955,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="70">
         <f>B8+1</f>
         <v>3</v>
@@ -10760,7 +10982,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f>B9+1</f>
         <v>4</v>
@@ -10800,17 +11022,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>28468000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="B11" s="70">
         <f>B10+1</f>
         <v>5</v>
@@ -10850,9 +11072,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -10870,17 +11092,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>17080800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -10921,12 +11143,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -10966,12 +11188,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -11011,17 +11233,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>16486200</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -11064,7 +11286,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -11107,7 +11329,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -11150,7 +11372,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -11183,7 +11405,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -11226,7 +11448,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -11269,7 +11491,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -11311,7 +11533,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -11354,7 +11576,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -11410,7 +11632,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -11449,7 +11671,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -11488,7 +11710,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -11507,7 +11729,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -11526,7 +11748,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -11624,18 +11846,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -11729,7 +11951,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -11775,7 +11997,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -11818,7 +12040,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -11861,7 +12083,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11901,23 +12123,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>20755000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -11935,17 +12157,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>12453000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -11986,12 +12208,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -12031,12 +12253,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -12076,17 +12298,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>12451000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -12125,7 +12347,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -12168,7 +12390,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -12211,7 +12433,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -12254,7 +12476,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -12296,7 +12518,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -12339,7 +12561,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -12378,7 +12600,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -12399,7 +12621,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -12438,7 +12660,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -12475,7 +12697,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -12512,7 +12734,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -12545,7 +12767,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -12564,7 +12786,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -12663,18 +12885,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -12768,7 +12990,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -12814,7 +13036,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -12858,7 +13080,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -12901,7 +13123,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12941,23 +13163,23 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>29815000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -12975,17 +13197,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>17889000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -13026,12 +13248,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -13049,12 +13271,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -13094,17 +13316,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17728000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -13147,7 +13369,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -13190,7 +13412,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -13233,7 +13455,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -13276,7 +13498,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -13319,7 +13541,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -13362,7 +13584,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -13401,7 +13623,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -13422,7 +13644,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -13461,7 +13683,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -13498,7 +13720,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -13535,7 +13757,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -13570,7 +13792,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -13611,7 +13833,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -13712,18 +13934,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -13816,7 +14038,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -13862,7 +14084,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -13906,7 +14128,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -13949,7 +14171,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -13989,17 +14211,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>29241000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -14007,9 +14229,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -14027,17 +14249,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>17544600</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -14078,12 +14300,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -14101,12 +14323,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="2">B14+1</f>
         <v>3</v>
@@ -14146,17 +14368,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17384600</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -14199,7 +14421,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -14242,7 +14464,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -14285,7 +14507,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="2"/>
         <v>7</v>
@@ -14328,7 +14550,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="2"/>
         <v>8</v>
@@ -14371,7 +14593,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="2"/>
         <v>9</v>
@@ -14414,7 +14636,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="2"/>
         <v>10</v>
@@ -14453,7 +14675,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -14474,7 +14696,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -14513,7 +14735,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -14551,7 +14773,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -14588,7 +14810,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -14622,7 +14844,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -14663,7 +14885,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -14735,32 +14957,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -15331,20 +15553,20 @@
       <c r="F25" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="201" t="s">
+      <c r="H25" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="201"/>
+      <c r="I25" s="244"/>
       <c r="J25" s="9">
         <f>SUM(H7:H1000)</f>
         <v>24820000</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(I7:I1000)</f>
         <v>14390000</v>
@@ -15487,18 +15709,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -15591,7 +15813,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -15639,7 +15861,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -15685,7 +15907,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -15728,7 +15950,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -15768,17 +15990,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>39465000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -15786,9 +16008,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -15806,17 +16028,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>23679000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -15857,12 +16079,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -15883,12 +16105,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -15928,17 +16150,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>23501000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -15981,7 +16203,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -16024,7 +16246,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -16067,7 +16289,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -16110,7 +16332,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -16153,7 +16375,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -16196,7 +16418,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16235,7 +16457,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -16256,7 +16478,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -16295,7 +16517,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -16333,7 +16555,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -16370,7 +16592,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -16405,7 +16627,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -16447,7 +16669,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -16547,18 +16769,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -16651,7 +16873,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -16697,7 +16919,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -16743,7 +16965,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -16786,7 +17008,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16826,17 +17048,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>28993000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -16844,9 +17066,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -16864,17 +17086,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>17395800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="206" t="s">
+      <c r="A13" s="249" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -16915,12 +17137,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206"/>
+      <c r="A14" s="249"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -16941,12 +17163,12 @@
       <c r="M14" s="76"/>
       <c r="N14" s="76"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="206"/>
+      <c r="A15" s="249"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B24" si="3">B14+1</f>
         <v>3</v>
@@ -16986,17 +17208,17 @@
       <c r="M15" s="79"/>
       <c r="N15" s="79"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>17285000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="206"/>
+      <c r="A16" s="249"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -17039,7 +17261,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="206"/>
+      <c r="A17" s="249"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -17084,7 +17306,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="206"/>
+      <c r="A18" s="249"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -17127,7 +17349,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="206"/>
+      <c r="A19" s="249"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -17170,7 +17392,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="206"/>
+      <c r="A20" s="249"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -17213,7 +17435,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="206"/>
+      <c r="A21" s="249"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -17256,7 +17478,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="206"/>
+      <c r="A22" s="249"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -17295,7 +17517,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="206"/>
+      <c r="A23" s="249"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -17316,7 +17538,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="206"/>
+      <c r="A24" s="249"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -17355,7 +17577,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="207" t="s">
+      <c r="A26" s="250" t="s">
         <v>136</v>
       </c>
       <c r="B26" s="64">
@@ -17393,7 +17615,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="208"/>
+      <c r="A27" s="251"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -17430,7 +17652,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="208"/>
+      <c r="A28" s="251"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -17465,7 +17687,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="208"/>
+      <c r="A29" s="251"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -17506,7 +17728,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="208"/>
+      <c r="A30" s="251"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -17606,18 +17828,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -17710,7 +17932,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -17756,7 +17978,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -17802,7 +18024,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -17845,7 +18067,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -17885,17 +18107,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>23968000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -17903,9 +18125,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -17923,17 +18145,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>14380800</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -17976,12 +18198,12 @@
       </c>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -18022,12 +18244,12 @@
       </c>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -18067,17 +18289,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14555400</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -18120,7 +18342,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -18159,7 +18381,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -18202,7 +18424,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -18245,7 +18467,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -18288,7 +18510,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -18327,7 +18549,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -18348,7 +18570,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -18369,7 +18591,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -18390,7 +18612,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -18411,7 +18633,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -18449,7 +18671,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -18486,7 +18708,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -18521,7 +18743,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -18562,7 +18784,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -18596,14 +18818,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="A13:A30"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="P10:Q11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="P12:Q14"/>
     <mergeCell ref="R12:R14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="A13:A30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -18661,18 +18883,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -18765,7 +18987,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -18807,7 +19029,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -18853,7 +19075,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -18896,7 +19118,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -18936,17 +19158,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>25750000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -18954,9 +19176,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -18974,17 +19196,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>15450000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -19025,12 +19247,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -19070,12 +19292,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B25" si="4">B14+1</f>
         <v>3</v>
@@ -19115,17 +19337,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>15330000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -19146,7 +19368,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -19189,7 +19411,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -19232,7 +19454,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -19275,7 +19497,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -19318,7 +19540,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -19357,7 +19579,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -19378,7 +19600,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -19415,7 +19637,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -19452,7 +19674,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -19489,7 +19711,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <v>1</v>
       </c>
@@ -19531,7 +19753,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f>B26+1</f>
         <v>2</v>
@@ -19554,7 +19776,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="70">
         <f>B27+1</f>
         <v>3</v>
@@ -19573,7 +19795,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f>B28+1</f>
         <v>4</v>
@@ -19592,7 +19814,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="70">
         <f>B29+1</f>
         <v>5</v>
@@ -19691,18 +19913,18 @@
     </row>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -19795,7 +20017,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -19841,7 +20063,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -19887,7 +20109,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="0">B8+1</f>
         <v>3</v>
@@ -19930,7 +20152,7 @@
       <c r="P9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -19970,17 +20192,17 @@
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="215" t="s">
+      <c r="P10" s="258" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="215"/>
-      <c r="R10" s="210">
+      <c r="Q10" s="258"/>
+      <c r="R10" s="253">
         <f>SUM(H7:H999)</f>
         <v>24922000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="146"/>
       <c r="I11" s="146"/>
       <c r="J11" s="146"/>
@@ -19988,9 +20210,9 @@
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
       <c r="O11" s="1"/>
-      <c r="P11" s="215"/>
-      <c r="Q11" s="215"/>
-      <c r="R11" s="210"/>
+      <c r="P11" s="258"/>
+      <c r="Q11" s="258"/>
+      <c r="R11" s="253"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -20008,17 +20230,17 @@
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="209" t="s">
+      <c r="P12" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210">
+      <c r="Q12" s="252"/>
+      <c r="R12" s="253">
         <f>SUM(I7:I999)</f>
         <v>14953200</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -20059,12 +20281,12 @@
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
+      <c r="P13" s="252"/>
+      <c r="Q13" s="252"/>
+      <c r="R13" s="253"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -20104,12 +20326,12 @@
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
+      <c r="P14" s="252"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="253"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -20149,17 +20371,17 @@
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
       <c r="O15" s="1"/>
-      <c r="P15" s="211" t="s">
+      <c r="P15" s="254" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="211"/>
+      <c r="Q15" s="254"/>
       <c r="R15" s="130">
         <f>SUM(J7:J98)</f>
         <v>14843000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -20180,7 +20402,7 @@
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -20223,7 +20445,7 @@
       <c r="P17" s="1"/>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -20268,7 +20490,7 @@
       <c r="P18" s="1"/>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -20313,7 +20535,7 @@
       <c r="P19" s="1"/>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -20356,7 +20578,7 @@
       <c r="P20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -20395,7 +20617,7 @@
       <c r="P21" s="1"/>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -20416,7 +20638,7 @@
       <c r="P22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -20455,7 +20677,7 @@
       <c r="P23" s="1"/>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -20494,7 +20716,7 @@
       <c r="P24" s="1"/>
     </row>
     <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -20531,7 +20753,7 @@
       <c r="P25" s="1"/>
     </row>
     <row r="26" spans="1:16" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -20574,7 +20796,7 @@
       <c r="P26" s="1"/>
     </row>
     <row r="27" spans="1:16" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -20597,7 +20819,7 @@
       <c r="P27" s="1"/>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -20616,7 +20838,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -20635,7 +20857,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -20710,18 +20932,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -20781,7 +21003,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -20826,7 +21048,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -20872,7 +21094,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="1">B8+1</f>
         <v>3</v>
@@ -20913,7 +21135,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -20952,26 +21174,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>21305000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -20988,17 +21210,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>12783000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -21038,12 +21260,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -21082,12 +21304,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="3">B14+1</f>
         <v>3</v>
@@ -21126,17 +21348,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12675000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -21158,7 +21380,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -21199,7 +21421,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -21246,7 +21468,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -21295,7 +21517,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -21336,7 +21558,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -21373,7 +21595,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -21395,7 +21617,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -21422,7 +21644,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -21449,7 +21671,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -21484,7 +21706,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -21525,7 +21747,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -21546,7 +21768,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -21565,7 +21787,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -21584,7 +21806,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -21649,18 +21871,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -21720,7 +21942,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -21765,7 +21987,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -21809,7 +22031,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -21850,7 +22072,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -21889,26 +22111,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>25660000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -21925,17 +22147,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>13375000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -21975,12 +22197,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -22019,12 +22241,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -22063,17 +22285,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13500000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -22098,7 +22320,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -22139,7 +22361,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -22191,7 +22413,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -22243,7 +22465,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -22284,7 +22506,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -22321,7 +22543,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -22346,7 +22568,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -22373,7 +22595,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -22400,7 +22622,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -22435,7 +22657,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -22476,7 +22698,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -22500,7 +22722,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -22519,7 +22741,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -22538,7 +22760,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -22603,18 +22825,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -22674,7 +22896,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -22721,7 +22943,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -22765,7 +22987,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -22806,7 +23028,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -22845,26 +23067,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>25245000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -22881,17 +23103,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>13121500</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -22931,12 +23153,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -22975,12 +23197,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -23019,17 +23241,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>13128000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -23054,7 +23276,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -23095,7 +23317,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -23141,7 +23363,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -23191,7 +23413,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -23232,7 +23454,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -23269,7 +23491,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -23294,7 +23516,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -23321,7 +23543,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -23348,7 +23570,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -23383,7 +23605,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -23424,7 +23646,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -23448,7 +23670,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -23467,7 +23689,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -23486,7 +23708,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -23551,18 +23773,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -23622,7 +23844,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -23669,7 +23891,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -23715,7 +23937,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -23758,7 +23980,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -23797,26 +24019,26 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>22790000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="H11" s="26"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -23833,17 +24055,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>12103000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -23883,12 +24105,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -23927,12 +24149,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="4">B14+1</f>
         <v>3</v>
@@ -23971,17 +24193,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>12000000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -24006,7 +24228,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -24047,7 +24269,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -24093,7 +24315,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
@@ -24143,7 +24365,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
@@ -24184,7 +24406,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
@@ -24221,7 +24443,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
@@ -24246,7 +24468,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
@@ -24273,7 +24495,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="4"/>
         <v>12</v>
@@ -24300,7 +24522,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="4"/>
         <v>13</v>
@@ -24335,7 +24557,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="4"/>
         <v>14</v>
@@ -24376,7 +24598,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="4"/>
         <v>15</v>
@@ -24400,7 +24622,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="4"/>
         <v>16</v>
@@ -24419,7 +24641,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="4"/>
         <v>17</v>
@@ -24438,7 +24660,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="4"/>
         <v>18</v>
@@ -24503,18 +24725,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -24574,7 +24796,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -24619,7 +24841,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -24655,7 +24877,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -24697,7 +24919,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -24738,17 +24960,17 @@
         <v>192</v>
       </c>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>18585000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -24761,9 +24983,9 @@
       <c r="L11" s="175"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -24780,17 +25002,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>10091000</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -24830,12 +25052,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -24874,12 +25096,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -24920,17 +25142,17 @@
         <v>191</v>
       </c>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>10021000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -24955,7 +25177,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -24996,7 +25218,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -25038,7 +25260,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -25090,7 +25312,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -25131,7 +25353,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -25166,7 +25388,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -25191,7 +25413,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -25218,7 +25440,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -25245,7 +25467,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -25280,7 +25502,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -25321,7 +25543,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -25345,7 +25567,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -25364,7 +25586,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -25383,7 +25605,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -25446,32 +25668,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -26140,20 +26362,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>29135000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>17346000</v>
@@ -26278,18 +26500,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:18" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:18" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -26349,7 +26571,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -26394,7 +26616,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -26430,7 +26652,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -26472,7 +26694,7 @@
       <c r="N9" s="79"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -26511,17 +26733,17 @@
       </c>
       <c r="M10" s="76"/>
       <c r="N10" s="76"/>
-      <c r="P10" s="218" t="s">
+      <c r="P10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="218"/>
-      <c r="R10" s="219">
+      <c r="Q10" s="261"/>
+      <c r="R10" s="262">
         <f>SUM(H7:H999)</f>
         <v>18425000</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -26534,9 +26756,9 @@
       <c r="L11" s="175"/>
       <c r="M11" s="79"/>
       <c r="N11" s="79"/>
-      <c r="P11" s="218"/>
-      <c r="Q11" s="218"/>
-      <c r="R11" s="219"/>
+      <c r="P11" s="261"/>
+      <c r="Q11" s="261"/>
+      <c r="R11" s="262"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -26553,17 +26775,17 @@
       <c r="L12" s="96"/>
       <c r="M12" s="97"/>
       <c r="N12" s="97"/>
-      <c r="P12" s="220" t="s">
+      <c r="P12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="Q12" s="220"/>
-      <c r="R12" s="219">
+      <c r="Q12" s="263"/>
+      <c r="R12" s="262">
         <f>SUM(I7:I999)</f>
         <v>10290500</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -26603,12 +26825,12 @@
       </c>
       <c r="M13" s="76"/>
       <c r="N13" s="76"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="220"/>
-      <c r="R13" s="219"/>
+      <c r="P13" s="263"/>
+      <c r="Q13" s="263"/>
+      <c r="R13" s="262"/>
     </row>
     <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -26647,12 +26869,12 @@
       </c>
       <c r="M14" s="79"/>
       <c r="N14" s="79"/>
-      <c r="P14" s="220"/>
-      <c r="Q14" s="220"/>
-      <c r="R14" s="219"/>
+      <c r="P14" s="263"/>
+      <c r="Q14" s="263"/>
+      <c r="R14" s="262"/>
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -26691,17 +26913,17 @@
       </c>
       <c r="M15" s="76"/>
       <c r="N15" s="85"/>
-      <c r="P15" s="221" t="s">
+      <c r="P15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="Q15" s="221"/>
+      <c r="Q15" s="264"/>
       <c r="R15" s="160">
         <f>SUM(J7:J98)</f>
         <v>10183000</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -26726,7 +26948,7 @@
       <c r="N16" s="76"/>
     </row>
     <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -26767,7 +26989,7 @@
       <c r="N17" s="85"/>
     </row>
     <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -26809,7 +27031,7 @@
       </c>
     </row>
     <row r="19" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -26861,7 +27083,7 @@
       </c>
     </row>
     <row r="20" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -26902,7 +27124,7 @@
       <c r="N20" s="76"/>
     </row>
     <row r="21" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -26933,7 +27155,7 @@
       <c r="N21" s="76"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -26958,7 +27180,7 @@
       <c r="N22" s="105"/>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -26994,7 +27216,7 @@
       <c r="N23" s="79"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -27021,7 +27243,7 @@
       <c r="N24" s="105"/>
     </row>
     <row r="25" spans="1:19" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -27056,7 +27278,7 @@
       <c r="N25" s="105"/>
     </row>
     <row r="26" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -27097,7 +27319,7 @@
       <c r="N26" s="76"/>
     </row>
     <row r="27" spans="1:19" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -27121,7 +27343,7 @@
       <c r="N27" s="76"/>
     </row>
     <row r="28" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -27140,7 +27362,7 @@
       <c r="N28" s="79"/>
     </row>
     <row r="29" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -27159,7 +27381,7 @@
       <c r="N29" s="76"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -27225,18 +27447,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -27290,7 +27512,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -27327,7 +27549,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -27365,7 +27587,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -27397,7 +27619,7 @@
       <c r="L9" s="79"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -27428,17 +27650,17 @@
       </c>
       <c r="K10" s="76"/>
       <c r="L10" s="76"/>
-      <c r="N10" s="218" t="s">
+      <c r="N10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="218"/>
-      <c r="P10" s="219">
+      <c r="O10" s="261"/>
+      <c r="P10" s="262">
         <f>SUM(H7:H999)</f>
         <v>12810000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="175"/>
@@ -27449,9 +27671,9 @@
       <c r="J11" s="175"/>
       <c r="K11" s="79"/>
       <c r="L11" s="79"/>
-      <c r="N11" s="218"/>
-      <c r="O11" s="218"/>
-      <c r="P11" s="219"/>
+      <c r="N11" s="261"/>
+      <c r="O11" s="261"/>
+      <c r="P11" s="262"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -27466,17 +27688,17 @@
       <c r="J12" s="96"/>
       <c r="K12" s="97"/>
       <c r="L12" s="97"/>
-      <c r="N12" s="220" t="s">
+      <c r="N12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="O12" s="220"/>
-      <c r="P12" s="219">
+      <c r="O12" s="263"/>
+      <c r="P12" s="262">
         <f>SUM(I7:I999)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -27510,12 +27732,12 @@
         <v>202</v>
       </c>
       <c r="L13" s="76"/>
-      <c r="N13" s="220"/>
-      <c r="O13" s="220"/>
-      <c r="P13" s="219"/>
+      <c r="N13" s="263"/>
+      <c r="O13" s="263"/>
+      <c r="P13" s="262"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -27546,12 +27768,12 @@
       </c>
       <c r="K14" s="79"/>
       <c r="L14" s="79"/>
-      <c r="N14" s="220"/>
-      <c r="O14" s="220"/>
-      <c r="P14" s="219"/>
+      <c r="N14" s="263"/>
+      <c r="O14" s="263"/>
+      <c r="P14" s="262"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -27582,17 +27804,17 @@
       </c>
       <c r="K15" s="76"/>
       <c r="L15" s="85"/>
-      <c r="N15" s="221" t="s">
+      <c r="N15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="O15" s="221"/>
+      <c r="O15" s="264"/>
       <c r="P15" s="160">
         <f>SUM(J7:J98)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -27615,7 +27837,7 @@
       <c r="L16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -27648,7 +27870,7 @@
       <c r="L17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -27682,7 +27904,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -27724,7 +27946,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -27757,7 +27979,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -27790,7 +28012,7 @@
       <c r="L21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -27813,7 +28035,7 @@
       <c r="L22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -27845,7 +28067,7 @@
       <c r="L23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -27878,7 +28100,7 @@
       <c r="L24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -27905,7 +28127,7 @@
       <c r="L25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -27938,7 +28160,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -27971,7 +28193,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -27988,7 +28210,7 @@
       <c r="L28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -28005,7 +28227,7 @@
       <c r="L29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -28069,18 +28291,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="198" t="s">
+      <c r="B3" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="198"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="198"/>
-      <c r="I3" s="198"/>
-      <c r="J3" s="198"/>
-      <c r="K3" s="198"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
     </row>
     <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
       <c r="C4" s="117"/>
@@ -28134,7 +28356,7 @@
       </c>
     </row>
     <row r="7" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="255" t="s">
         <v>119</v>
       </c>
       <c r="B7" s="64">
@@ -28171,7 +28393,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="213"/>
+      <c r="A8" s="256"/>
       <c r="B8" s="64">
         <f>B7+1</f>
         <v>2</v>
@@ -28199,7 +28421,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="213"/>
+      <c r="A9" s="256"/>
       <c r="B9" s="64">
         <f t="shared" ref="B9:B10" si="2">B8+1</f>
         <v>3</v>
@@ -28231,7 +28453,7 @@
       <c r="L9" s="79"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="213"/>
+      <c r="A10" s="256"/>
       <c r="B10" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -28262,17 +28484,17 @@
       </c>
       <c r="K10" s="76"/>
       <c r="L10" s="76"/>
-      <c r="N10" s="218" t="s">
+      <c r="N10" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="218"/>
-      <c r="P10" s="219">
+      <c r="O10" s="261"/>
+      <c r="P10" s="262">
         <f>SUM(F7:F999)</f>
         <v>25582000</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="214"/>
+      <c r="A11" s="257"/>
       <c r="C11" s="175"/>
       <c r="D11" s="175"/>
       <c r="E11" s="195"/>
@@ -28283,9 +28505,9 @@
       <c r="J11" s="175"/>
       <c r="K11" s="79"/>
       <c r="L11" s="79"/>
-      <c r="N11" s="218"/>
-      <c r="O11" s="218"/>
-      <c r="P11" s="219"/>
+      <c r="N11" s="261"/>
+      <c r="O11" s="261"/>
+      <c r="P11" s="262"/>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="107"/>
@@ -28300,17 +28522,17 @@
       <c r="J12" s="96"/>
       <c r="K12" s="97"/>
       <c r="L12" s="97"/>
-      <c r="N12" s="220" t="s">
+      <c r="N12" s="263" t="s">
         <v>143</v>
       </c>
-      <c r="O12" s="220"/>
-      <c r="P12" s="219">
+      <c r="O12" s="263"/>
+      <c r="P12" s="262">
         <f>SUM(G7:G999)</f>
         <v>13354000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="216" t="s">
+      <c r="A13" s="259" t="s">
         <v>118</v>
       </c>
       <c r="B13" s="64">
@@ -28342,12 +28564,12 @@
       </c>
       <c r="K13" s="76"/>
       <c r="L13" s="76"/>
-      <c r="N13" s="220"/>
-      <c r="O13" s="220"/>
-      <c r="P13" s="219"/>
+      <c r="N13" s="263"/>
+      <c r="O13" s="263"/>
+      <c r="P13" s="262"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="217"/>
+      <c r="A14" s="260"/>
       <c r="B14" s="64">
         <f>B13+1</f>
         <v>2</v>
@@ -28378,12 +28600,12 @@
       </c>
       <c r="K14" s="79"/>
       <c r="L14" s="79"/>
-      <c r="N14" s="220"/>
-      <c r="O14" s="220"/>
-      <c r="P14" s="219"/>
+      <c r="N14" s="263"/>
+      <c r="O14" s="263"/>
+      <c r="P14" s="262"/>
     </row>
     <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="217"/>
+      <c r="A15" s="260"/>
       <c r="B15" s="64">
         <f t="shared" ref="B15:B30" si="5">B14+1</f>
         <v>3</v>
@@ -28410,17 +28632,17 @@
         <v>210</v>
       </c>
       <c r="L15" s="85"/>
-      <c r="N15" s="221" t="s">
+      <c r="N15" s="264" t="s">
         <v>117</v>
       </c>
-      <c r="O15" s="221"/>
+      <c r="O15" s="264"/>
       <c r="P15" s="160">
         <f>SUM(H7:H999)</f>
         <v>13332000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="217"/>
+      <c r="A16" s="260"/>
       <c r="B16" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -28443,7 +28665,7 @@
       <c r="L16" s="76"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="217"/>
+      <c r="A17" s="260"/>
       <c r="B17" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -28476,7 +28698,7 @@
       <c r="L17" s="85"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="217"/>
+      <c r="A18" s="260"/>
       <c r="B18" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -28516,7 +28738,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="217"/>
+      <c r="A19" s="260"/>
       <c r="B19" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
@@ -28560,7 +28782,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="217"/>
+      <c r="A20" s="260"/>
       <c r="B20" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
@@ -28593,7 +28815,7 @@
       <c r="L20" s="76"/>
     </row>
     <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="217"/>
+      <c r="A21" s="260"/>
       <c r="B21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
@@ -28622,7 +28844,7 @@
       <c r="L21" s="76"/>
     </row>
     <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="217"/>
+      <c r="A22" s="260"/>
       <c r="B22" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -28645,7 +28867,7 @@
       <c r="L22" s="105"/>
     </row>
     <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="217"/>
+      <c r="A23" s="260"/>
       <c r="B23" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -28677,7 +28899,7 @@
       <c r="L23" s="79"/>
     </row>
     <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="217"/>
+      <c r="A24" s="260"/>
       <c r="B24" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -28712,7 +28934,7 @@
       <c r="L24" s="105"/>
     </row>
     <row r="25" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="217"/>
+      <c r="A25" s="260"/>
       <c r="B25" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -28743,7 +28965,7 @@
       <c r="L25" s="105"/>
     </row>
     <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="217"/>
+      <c r="A26" s="260"/>
       <c r="B26" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -28776,7 +28998,7 @@
       <c r="L26" s="76"/>
     </row>
     <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="217"/>
+      <c r="A27" s="260"/>
       <c r="B27" s="64">
         <f t="shared" si="5"/>
         <v>15</v>
@@ -28809,7 +29031,7 @@
       <c r="L27" s="76"/>
     </row>
     <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="217"/>
+      <c r="A28" s="260"/>
       <c r="B28" s="64">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -28826,7 +29048,7 @@
       <c r="L28" s="79"/>
     </row>
     <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="217"/>
+      <c r="A29" s="260"/>
       <c r="B29" s="64">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -28843,7 +29065,7 @@
       <c r="L29" s="76"/>
     </row>
     <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="217"/>
+      <c r="A30" s="260"/>
       <c r="B30" s="64">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -28873,6 +29095,1341 @@
     <mergeCell ref="N12:O14"/>
     <mergeCell ref="P12:P14"/>
     <mergeCell ref="A13:A30"/>
+    <mergeCell ref="N15:O15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBEB86F-A8DD-42F9-B2B2-37DBDB0C26B6}">
+  <dimension ref="A3:Q47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="37.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="31.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="18.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="21.28515625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="241" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="241"/>
+      <c r="D3" s="241"/>
+      <c r="E3" s="241"/>
+      <c r="F3" s="241"/>
+      <c r="G3" s="241"/>
+      <c r="H3" s="241"/>
+      <c r="I3" s="241"/>
+      <c r="J3" s="241"/>
+      <c r="K3" s="241"/>
+    </row>
+    <row r="4" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="G4" s="116" t="s">
+        <v>215</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+    </row>
+    <row r="5" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:16" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="105"/>
+      <c r="B6" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="158" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="158" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="158" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="158" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="159" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="158" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="158" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="158" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="158" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="158" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="255" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="66"/>
+      <c r="E7" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="68">
+        <v>1200000</v>
+      </c>
+      <c r="G7" s="68">
+        <f>IF(F7="",0,IF(F7&gt;1700000,F7*O$19,F7*O$18))</f>
+        <v>720000</v>
+      </c>
+      <c r="H7" s="68">
+        <v>720000</v>
+      </c>
+      <c r="I7" s="68">
+        <f>G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="224"/>
+      <c r="L7" s="76"/>
+      <c r="N7" s="88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="256"/>
+      <c r="B8" s="64">
+        <f>B7+1</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="75"/>
+      <c r="E8" s="193" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="68">
+        <v>900000</v>
+      </c>
+      <c r="G8" s="68">
+        <f>IF(F8="",0,IF(F8&gt;1700000,F8*O$19,F8*O$18))</f>
+        <v>540000</v>
+      </c>
+      <c r="H8" s="68">
+        <v>450000</v>
+      </c>
+      <c r="I8" s="68">
+        <f t="shared" ref="I8:I10" si="0">G8-H8</f>
+        <v>90000</v>
+      </c>
+      <c r="J8" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="225"/>
+      <c r="L8" s="76"/>
+      <c r="N8" s="82" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="256"/>
+      <c r="B9" s="64">
+        <f t="shared" ref="B9:B18" si="1">B8+1</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="66"/>
+      <c r="E9" s="192" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="68">
+        <v>800000</v>
+      </c>
+      <c r="G9" s="68">
+        <f>IF(F9="",0,IF(F9&gt;1700000,F9*O$19,F9*O$18))</f>
+        <v>480000</v>
+      </c>
+      <c r="H9" s="74">
+        <v>500000</v>
+      </c>
+      <c r="I9" s="68">
+        <v>0</v>
+      </c>
+      <c r="J9" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="225"/>
+      <c r="L9" s="79"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="256"/>
+      <c r="B10" s="64">
+        <f>B9+1</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="73"/>
+      <c r="E10" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="74">
+        <v>750000</v>
+      </c>
+      <c r="G10" s="68">
+        <f>IF(F10="",0,IF(F10&gt;1700000,F10*O$19,F10*O$18))</f>
+        <v>450000</v>
+      </c>
+      <c r="H10" s="74"/>
+      <c r="I10" s="68">
+        <f t="shared" si="0"/>
+        <v>450000</v>
+      </c>
+      <c r="J10" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="225"/>
+      <c r="L10" s="76"/>
+      <c r="N10" s="261" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="261"/>
+      <c r="P10" s="262">
+        <f>SUM(F7:F1006)</f>
+        <v>27514000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="256"/>
+      <c r="B11" s="64">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>220</v>
+      </c>
+      <c r="D11" s="73"/>
+      <c r="E11" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="74"/>
+      <c r="G11" s="68">
+        <f>IF(F11="",0,IF(F11&gt;1700000,F11*O$19,F11*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="74"/>
+      <c r="I11" s="68">
+        <f t="shared" ref="I11:I18" si="2">G11-H11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="131"/>
+      <c r="K11" s="240" t="s">
+        <v>221</v>
+      </c>
+      <c r="L11" s="76"/>
+      <c r="N11" s="261"/>
+      <c r="O11" s="261"/>
+      <c r="P11" s="262"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="256"/>
+      <c r="B12" s="64">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="73"/>
+      <c r="E12" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="74"/>
+      <c r="G12" s="68">
+        <f t="shared" ref="G12:G18" si="3">IF(F12="",0,IF(F12&gt;1700000,F12*O$19,F12*O$18))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="74"/>
+      <c r="I12" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="131"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="76"/>
+      <c r="N12" s="263" t="s">
+        <v>143</v>
+      </c>
+      <c r="O12" s="263"/>
+      <c r="P12" s="262">
+        <f>SUM(G7:G1006)</f>
+        <v>14849900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="256"/>
+      <c r="B13" s="64">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="73"/>
+      <c r="E13" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="74"/>
+      <c r="G13" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="74"/>
+      <c r="I13" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="131"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="76"/>
+      <c r="N13" s="263"/>
+      <c r="O13" s="263"/>
+      <c r="P13" s="262"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="256"/>
+      <c r="B14" s="64">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="73"/>
+      <c r="E14" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="74"/>
+      <c r="G14" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="74"/>
+      <c r="I14" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="131"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="76"/>
+      <c r="N14" s="263"/>
+      <c r="O14" s="263"/>
+      <c r="P14" s="262"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="256"/>
+      <c r="B15" s="64">
+        <f>B14+1</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="73"/>
+      <c r="E15" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="74"/>
+      <c r="G15" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="74"/>
+      <c r="I15" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="131"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="76"/>
+      <c r="N15" s="264" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="264"/>
+      <c r="P15" s="160">
+        <f>SUM(H7:H1006)</f>
+        <v>13888000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="256"/>
+      <c r="B16" s="64">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="73"/>
+      <c r="E16" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="74"/>
+      <c r="G16" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="74"/>
+      <c r="I16" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="131"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="76"/>
+    </row>
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="256"/>
+      <c r="B17" s="64">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="73"/>
+      <c r="E17" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="74"/>
+      <c r="G17" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="74"/>
+      <c r="I17" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="131"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="76"/>
+    </row>
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="256"/>
+      <c r="B18" s="64">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="73"/>
+      <c r="E18" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="74"/>
+      <c r="G18" s="68">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="74"/>
+      <c r="I18" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="131"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="76"/>
+      <c r="N18" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="162">
+        <v>0.6</v>
+      </c>
+      <c r="Q18" s="164" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="257"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="147"/>
+      <c r="I19" s="123"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="226"/>
+      <c r="L19" s="97"/>
+      <c r="N19" s="157" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="163">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="164" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="265" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="64">
+        <v>1</v>
+      </c>
+      <c r="C20" s="198" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="199"/>
+      <c r="E20" s="199" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="200">
+        <v>1900000</v>
+      </c>
+      <c r="G20" s="200">
+        <f t="shared" ref="G20:G47" si="4">IF(F20="",0,IF(F20&gt;=1700000,F20*O$19,F20*O$18))</f>
+        <v>950000</v>
+      </c>
+      <c r="H20" s="200">
+        <v>950000</v>
+      </c>
+      <c r="I20" s="200">
+        <f t="shared" ref="I20:I37" si="5">G20-H20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="228" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="202"/>
+    </row>
+    <row r="21" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="266"/>
+      <c r="B21" s="64">
+        <f>B20+1</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="203" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="204"/>
+      <c r="E21" s="204" t="s">
+        <v>206</v>
+      </c>
+      <c r="F21" s="205">
+        <v>1304000</v>
+      </c>
+      <c r="G21" s="200">
+        <f t="shared" si="4"/>
+        <v>782400</v>
+      </c>
+      <c r="H21" s="205">
+        <v>783000</v>
+      </c>
+      <c r="I21" s="200">
+        <f t="shared" si="5"/>
+        <v>-600</v>
+      </c>
+      <c r="J21" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="228" t="s">
+        <v>218</v>
+      </c>
+      <c r="L21" s="206"/>
+    </row>
+    <row r="22" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="266"/>
+      <c r="B22" s="64">
+        <f t="shared" ref="B22:B47" si="6">B21+1</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="198" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="207"/>
+      <c r="E22" s="207" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="200">
+        <v>1720000</v>
+      </c>
+      <c r="G22" s="200">
+        <f t="shared" si="4"/>
+        <v>860000</v>
+      </c>
+      <c r="H22" s="205">
+        <v>860000</v>
+      </c>
+      <c r="I22" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="228" t="s">
+        <v>218</v>
+      </c>
+      <c r="L22" s="208"/>
+    </row>
+    <row r="23" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="266"/>
+      <c r="B23" s="64">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="C23" s="233"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="235"/>
+      <c r="G23" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="235"/>
+      <c r="I23" s="235">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="236"/>
+      <c r="K23" s="237"/>
+      <c r="L23" s="202"/>
+    </row>
+    <row r="24" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="266"/>
+      <c r="B24" s="64">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="C24" s="198" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="207"/>
+      <c r="E24" s="207" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="200">
+        <v>1756000</v>
+      </c>
+      <c r="G24" s="200">
+        <f t="shared" si="4"/>
+        <v>878000</v>
+      </c>
+      <c r="H24" s="205">
+        <v>878000</v>
+      </c>
+      <c r="I24" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" s="229" t="s">
+        <v>218</v>
+      </c>
+      <c r="L24" s="208"/>
+    </row>
+    <row r="25" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="266"/>
+      <c r="B25" s="64">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="C25" s="198" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="207"/>
+      <c r="E25" s="207" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="200">
+        <v>2901000</v>
+      </c>
+      <c r="G25" s="200">
+        <f t="shared" si="4"/>
+        <v>1450500</v>
+      </c>
+      <c r="H25" s="205">
+        <v>1451000</v>
+      </c>
+      <c r="I25" s="200">
+        <f t="shared" si="5"/>
+        <v>-500</v>
+      </c>
+      <c r="J25" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K25" s="210"/>
+      <c r="L25" s="202"/>
+    </row>
+    <row r="26" spans="1:17" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="266"/>
+      <c r="B26" s="64">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="C26" s="198" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="202"/>
+      <c r="E26" s="202" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="200">
+        <v>1830000</v>
+      </c>
+      <c r="G26" s="200">
+        <f t="shared" si="4"/>
+        <v>915000</v>
+      </c>
+      <c r="H26" s="200">
+        <v>920000</v>
+      </c>
+      <c r="I26" s="200">
+        <f t="shared" si="5"/>
+        <v>-5000</v>
+      </c>
+      <c r="J26" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K26" s="229" t="s">
+        <v>218</v>
+      </c>
+      <c r="L26" s="202"/>
+    </row>
+    <row r="27" spans="1:17" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="266"/>
+      <c r="B27" s="64">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="C27" s="203" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="206"/>
+      <c r="E27" s="202" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="205">
+        <v>750000</v>
+      </c>
+      <c r="G27" s="200">
+        <f t="shared" si="4"/>
+        <v>450000</v>
+      </c>
+      <c r="H27" s="200"/>
+      <c r="I27" s="200">
+        <f t="shared" si="5"/>
+        <v>450000</v>
+      </c>
+      <c r="J27" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" s="211"/>
+      <c r="L27" s="202"/>
+    </row>
+    <row r="28" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="266"/>
+      <c r="B28" s="64">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="203" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="213"/>
+      <c r="E28" s="212" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="205">
+        <v>1010000</v>
+      </c>
+      <c r="G28" s="200">
+        <f t="shared" si="4"/>
+        <v>606000</v>
+      </c>
+      <c r="H28" s="205">
+        <v>606000</v>
+      </c>
+      <c r="I28" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28" s="219"/>
+      <c r="L28" s="202"/>
+    </row>
+    <row r="29" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="266"/>
+      <c r="B29" s="64">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="C29" s="238"/>
+      <c r="D29" s="238"/>
+      <c r="E29" s="238"/>
+      <c r="F29" s="239"/>
+      <c r="G29" s="235">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="239"/>
+      <c r="I29" s="235">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="238"/>
+      <c r="K29" s="214"/>
+      <c r="L29" s="222"/>
+    </row>
+    <row r="30" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="266"/>
+      <c r="B30" s="64">
+        <f t="shared" si="6"/>
+        <v>11</v>
+      </c>
+      <c r="C30" s="215" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="199"/>
+      <c r="E30" s="207" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="216">
+        <v>1758000</v>
+      </c>
+      <c r="G30" s="200">
+        <f t="shared" si="4"/>
+        <v>879000</v>
+      </c>
+      <c r="H30" s="217">
+        <v>879000</v>
+      </c>
+      <c r="I30" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K30" s="230" t="s">
+        <v>218</v>
+      </c>
+      <c r="L30" s="206"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="266"/>
+      <c r="B31" s="64">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="C31" s="215" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="207"/>
+      <c r="E31" s="202" t="s">
+        <v>207</v>
+      </c>
+      <c r="F31" s="216">
+        <v>2925000</v>
+      </c>
+      <c r="G31" s="200">
+        <f t="shared" si="4"/>
+        <v>1462500</v>
+      </c>
+      <c r="H31" s="216">
+        <v>1462000</v>
+      </c>
+      <c r="I31" s="200">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="J31" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K31" s="230" t="s">
+        <v>218</v>
+      </c>
+      <c r="L31" s="222"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="266"/>
+      <c r="B32" s="64">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="C32" s="215" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="204"/>
+      <c r="E32" s="207" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="200">
+        <v>990000</v>
+      </c>
+      <c r="G32" s="200">
+        <f t="shared" si="4"/>
+        <v>594000</v>
+      </c>
+      <c r="H32" s="200">
+        <v>594000</v>
+      </c>
+      <c r="I32" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K32" s="214"/>
+      <c r="L32" s="222"/>
+    </row>
+    <row r="33" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="266"/>
+      <c r="B33" s="64">
+        <f t="shared" si="6"/>
+        <v>14</v>
+      </c>
+      <c r="C33" s="198" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="199"/>
+      <c r="E33" s="199" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="218">
+        <v>1795000</v>
+      </c>
+      <c r="G33" s="200">
+        <f t="shared" si="4"/>
+        <v>897500</v>
+      </c>
+      <c r="H33" s="216">
+        <v>900000</v>
+      </c>
+      <c r="I33" s="200">
+        <f t="shared" si="5"/>
+        <v>-2500</v>
+      </c>
+      <c r="J33" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K33" s="230" t="s">
+        <v>218</v>
+      </c>
+      <c r="L33" s="202"/>
+    </row>
+    <row r="34" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="266"/>
+      <c r="B34" s="64">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="C34" s="203" t="s">
+        <v>217</v>
+      </c>
+      <c r="D34" s="213"/>
+      <c r="E34" s="207" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" s="205">
+        <v>255000</v>
+      </c>
+      <c r="G34" s="200">
+        <f t="shared" si="4"/>
+        <v>153000</v>
+      </c>
+      <c r="H34" s="205">
+        <v>153000</v>
+      </c>
+      <c r="I34" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K34" s="220"/>
+      <c r="L34" s="202"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="266"/>
+      <c r="B35" s="64">
+        <f t="shared" si="6"/>
+        <v>16</v>
+      </c>
+      <c r="C35" s="222" t="s">
+        <v>216</v>
+      </c>
+      <c r="D35" s="222"/>
+      <c r="E35" s="207" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="223">
+        <v>1340000</v>
+      </c>
+      <c r="G35" s="200">
+        <f t="shared" si="4"/>
+        <v>804000</v>
+      </c>
+      <c r="H35" s="223">
+        <v>804000</v>
+      </c>
+      <c r="I35" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K35" s="221"/>
+      <c r="L35" s="206"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="266"/>
+      <c r="B36" s="64">
+        <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="C36" s="222" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="105"/>
+      <c r="E36" s="207" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="223">
+        <v>1630000</v>
+      </c>
+      <c r="G36" s="200">
+        <f t="shared" si="4"/>
+        <v>978000</v>
+      </c>
+      <c r="H36" s="223">
+        <v>978000</v>
+      </c>
+      <c r="I36" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="201" t="s">
+        <v>69</v>
+      </c>
+      <c r="K36" s="225"/>
+      <c r="L36" s="76"/>
+    </row>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="266"/>
+      <c r="B37" s="64">
+        <f t="shared" si="6"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="231"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="232"/>
+      <c r="G37" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="216"/>
+      <c r="I37" s="200">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="209"/>
+      <c r="K37" s="227"/>
+      <c r="L37" s="79"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="266"/>
+      <c r="B38" s="64">
+        <f t="shared" si="6"/>
+        <v>19</v>
+      </c>
+      <c r="C38" s="231"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="232"/>
+      <c r="G38" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="216"/>
+      <c r="I38" s="200">
+        <f t="shared" ref="I38:I40" si="7">G38-H38</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="209"/>
+      <c r="K38" s="227"/>
+      <c r="L38" s="79"/>
+    </row>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="266"/>
+      <c r="B39" s="64">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="231"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="216"/>
+      <c r="I39" s="200">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="209"/>
+      <c r="K39" s="227"/>
+      <c r="L39" s="79"/>
+    </row>
+    <row r="40" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="266"/>
+      <c r="B40" s="64">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="C40" s="231"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="232"/>
+      <c r="G40" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="216"/>
+      <c r="I40" s="200">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="209"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="79"/>
+    </row>
+    <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="266"/>
+      <c r="B41" s="64">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="C41" s="231"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="232"/>
+      <c r="G41" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="216"/>
+      <c r="I41" s="200">
+        <f t="shared" ref="I41:I43" si="8">G41-H41</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="209"/>
+      <c r="K41" s="227"/>
+      <c r="L41" s="79"/>
+    </row>
+    <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="266"/>
+      <c r="B42" s="64">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="C42" s="231"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="216"/>
+      <c r="I42" s="200">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="209"/>
+      <c r="K42" s="227"/>
+      <c r="L42" s="79"/>
+    </row>
+    <row r="43" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="266"/>
+      <c r="B43" s="64">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="C43" s="231"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="232"/>
+      <c r="G43" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="216"/>
+      <c r="I43" s="200">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="209"/>
+      <c r="K43" s="227"/>
+      <c r="L43" s="79"/>
+    </row>
+    <row r="44" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="266"/>
+      <c r="B44" s="64">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="C44" s="231"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="232"/>
+      <c r="G44" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="216"/>
+      <c r="I44" s="200">
+        <f t="shared" ref="I44:I47" si="9">G44-H44</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="209"/>
+      <c r="K44" s="227"/>
+      <c r="L44" s="79"/>
+    </row>
+    <row r="45" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="266"/>
+      <c r="B45" s="64">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="C45" s="231"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="232"/>
+      <c r="G45" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="216"/>
+      <c r="I45" s="200">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="209"/>
+      <c r="K45" s="227"/>
+      <c r="L45" s="79"/>
+    </row>
+    <row r="46" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="266"/>
+      <c r="B46" s="64">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="C46" s="231"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="232"/>
+      <c r="G46" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="216"/>
+      <c r="I46" s="200">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="209"/>
+      <c r="K46" s="227"/>
+      <c r="L46" s="79"/>
+    </row>
+    <row r="47" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="266"/>
+      <c r="B47" s="64">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="C47" s="231"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="232"/>
+      <c r="G47" s="200">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H47" s="216"/>
+      <c r="I47" s="200">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="209"/>
+      <c r="K47" s="227"/>
+      <c r="L47" s="79"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A20:A47"/>
+    <mergeCell ref="A7:A19"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="N10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="N12:O14"/>
+    <mergeCell ref="P12:P14"/>
     <mergeCell ref="N15:O15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28903,32 +30460,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -29593,20 +31150,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32170000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19075000</v>
@@ -29727,32 +31284,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -30404,20 +31961,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30806000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18342000</v>
@@ -30538,32 +32095,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -31210,20 +32767,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>30762000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18280000</v>
@@ -31347,32 +32904,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -32025,20 +33582,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31566000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18200000</v>
@@ -32162,32 +33719,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:13" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -32837,20 +34394,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>31500000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>18612000</v>
@@ -32976,32 +34533,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="241"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="241"/>
+      <c r="I2" s="241"/>
+      <c r="J2" s="241"/>
+      <c r="K2" s="241"/>
     </row>
     <row r="3" spans="2:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="242" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="200"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="200"/>
-      <c r="H3" s="200"/>
-      <c r="I3" s="200"/>
-      <c r="J3" s="200"/>
-      <c r="K3" s="200"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J4" s="26"/>
@@ -33663,20 +35220,20 @@
       <c r="F26" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="201" t="s">
+      <c r="H26" s="244" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="201"/>
+      <c r="I26" s="244"/>
       <c r="J26" s="9">
         <f>SUM(H7:H1001)</f>
         <v>32130000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="22.5" x14ac:dyDescent="0.3">
-      <c r="H27" s="201" t="s">
+      <c r="H27" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="201"/>
+      <c r="I27" s="244"/>
       <c r="J27" s="9">
         <f>SUM(I7:I1001)</f>
         <v>19110000</v>

--- a/Theo dõi/T1 2026 02-01.xlsx
+++ b/Theo dõi/T1 2026 02-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Theo dõi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384963EE-C5D9-4ED6-9C93-10A7451DFD02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E839A824-428D-4252-A350-E3C52C5E1DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="579" firstSheet="18" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18818,14 +18818,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="P10:Q11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="P12:Q14"/>
     <mergeCell ref="R12:R14"/>
     <mergeCell ref="P15:Q15"/>
     <mergeCell ref="A13:A30"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="P10:Q11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -29318,13 +29318,15 @@
         <f>IF(F10="",0,IF(F10&gt;1700000,F10*O$19,F10*O$18))</f>
         <v>450000</v>
       </c>
-      <c r="H10" s="74"/>
+      <c r="H10" s="74">
+        <v>450000</v>
+      </c>
       <c r="I10" s="68">
         <f t="shared" si="0"/>
-        <v>450000</v>
-      </c>
-      <c r="J10" s="82" t="s">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="J10" s="88" t="s">
+        <v>26</v>
       </c>
       <c r="K10" s="225"/>
       <c r="L10" s="76"/>
@@ -29496,7 +29498,7 @@
       <c r="O15" s="264"/>
       <c r="P15" s="160">
         <f>SUM(H7:H1006)</f>
-        <v>13888000</v>
+        <v>14838000</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -29864,13 +29866,15 @@
         <f t="shared" si="4"/>
         <v>450000</v>
       </c>
-      <c r="H27" s="200"/>
+      <c r="H27" s="200">
+        <v>500000</v>
+      </c>
       <c r="I27" s="200">
         <f t="shared" si="5"/>
-        <v>450000</v>
-      </c>
-      <c r="J27" s="82" t="s">
-        <v>72</v>
+        <v>-50000</v>
+      </c>
+      <c r="J27" s="201" t="s">
+        <v>69</v>
       </c>
       <c r="K27" s="211"/>
       <c r="L27" s="202"/>
